--- a/diseases/d058/2010-2014.xlsx
+++ b/diseases/d058/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1069,6 +1079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1217,6 +1232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1362,6 +1382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1510,6 +1535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1658,6 +1688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1803,6 +1838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1951,6 +1991,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2099,6 +2144,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2244,6 +2294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2392,6 +2447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2540,6 +2600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2685,6 +2750,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2833,6 +2903,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2981,6 +3056,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3126,6 +3206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3274,6 +3359,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3422,6 +3512,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3567,6 +3662,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3715,6 +3815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3863,6 +3968,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4008,6 +4118,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4156,6 +4271,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4304,6 +4424,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4449,6 +4574,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4597,6 +4727,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4745,6 +4880,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4890,6 +5030,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5038,6 +5183,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5186,6 +5336,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5331,6 +5486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5479,6 +5639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5627,6 +5792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5772,6 +5942,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5920,6 +6095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6068,6 +6248,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6213,6 +6398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6361,6 +6551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6509,6 +6704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6654,6 +6854,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6802,6 +7007,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6950,6 +7160,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7095,6 +7310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7243,6 +7463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7391,6 +7616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7536,6 +7766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7684,6 +7919,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7832,6 +8072,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7977,6 +8222,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8125,6 +8375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8273,6 +8528,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8418,6 +8678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8566,6 +8831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8714,6 +8984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8859,6 +9134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9007,6 +9287,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9155,6 +9440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9300,6 +9590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9448,6 +9743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9596,6 +9896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9741,6 +10046,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9889,6 +10199,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10037,6 +10352,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10182,6 +10502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10330,6 +10655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10478,6 +10808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10623,6 +10958,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10771,6 +11111,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10919,6 +11264,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11064,6 +11414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11212,6 +11567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11360,6 +11720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11505,6 +11870,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11653,6 +12023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11801,6 +12176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11946,6 +12326,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12094,6 +12479,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12242,6 +12632,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12387,6 +12782,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12535,6 +12935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12683,6 +13088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12828,6 +13238,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12976,6 +13391,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13124,6 +13544,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13269,6 +13694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13417,6 +13847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13565,6 +14000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13710,6 +14150,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13858,6 +14303,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14006,6 +14456,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14151,6 +14606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14299,6 +14759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14447,6 +14912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14592,6 +15062,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14740,6 +15215,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14888,6 +15368,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15033,6 +15518,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15181,6 +15671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15773,6 +16268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15918,6 +16418,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16066,6 +16571,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16806,6 +17316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16951,6 +17466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17099,6 +17619,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17987,6 +18512,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18132,6 +18662,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18280,6 +18815,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19020,6 +19560,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19165,6 +19710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19313,6 +19863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20053,6 +20608,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20346,6 +20906,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20494,6 +21059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21086,6 +21656,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21379,6 +21954,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21527,6 +22107,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22267,6 +22852,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22412,6 +23002,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22560,6 +23155,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23300,6 +23900,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23445,6 +24050,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23593,6 +24203,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24481,6 +25096,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24626,6 +25246,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24774,6 +25399,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25514,6 +26144,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25659,6 +26294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25807,6 +26447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26547,6 +27192,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26692,6 +27342,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26840,6 +27495,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27728,6 +28388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27873,6 +28538,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28021,6 +28691,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28761,6 +29436,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28906,6 +29586,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29054,6 +29739,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29794,6 +30484,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30087,6 +30782,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30235,6 +30935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30975,6 +31680,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31120,6 +31830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31268,6 +31983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32008,6 +32728,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32153,6 +32878,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32301,6 +33031,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33189,6 +33924,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33334,6 +34074,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33482,6 +34227,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34222,6 +34972,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34367,6 +35122,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34515,6 +35275,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35255,6 +36020,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35400,6 +36170,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35548,6 +36323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36288,6 +37068,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36433,6 +37218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36581,6 +37371,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37469,6 +38264,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37614,6 +38414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37762,6 +38567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38502,6 +39312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38647,6 +39462,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38795,6 +39615,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39535,6 +40360,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39828,6 +40658,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39976,6 +40811,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40716,6 +41556,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40861,6 +41706,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41009,6 +41859,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41749,6 +42604,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41894,6 +42754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42042,6 +42907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42930,6 +43800,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43075,6 +43950,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43223,6 +44103,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43963,6 +44848,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44108,6 +44998,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44254,6 +45149,11 @@
       <c r="S297" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO297" t="inlineStr">

--- a/diseases/d058/2010-2014.xlsx
+++ b/diseases/d058/2010-2014.xlsx
@@ -15824,28 +15824,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
@@ -15972,28 +15986,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
@@ -16120,28 +16148,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -16724,28 +16766,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -16872,28 +16928,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
@@ -17020,28 +17090,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -17168,28 +17252,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -17772,28 +17870,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
@@ -17920,28 +18032,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
@@ -18068,28 +18194,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
@@ -18216,28 +18356,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
@@ -18364,28 +18518,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
@@ -18968,28 +19136,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -19116,28 +19298,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -19264,28 +19460,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
@@ -19412,28 +19622,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
@@ -20016,28 +20240,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
@@ -20164,28 +20402,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS130" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
@@ -20312,28 +20564,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -20460,28 +20726,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -20761,28 +21041,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
@@ -21212,28 +21506,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -21360,28 +21668,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -21508,28 +21830,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -21809,28 +22145,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -22260,28 +22610,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
@@ -22408,28 +22772,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
@@ -22556,28 +22934,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
@@ -22704,28 +23096,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
@@ -23308,28 +23714,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
@@ -23456,28 +23876,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
@@ -23604,28 +24038,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
@@ -23752,28 +24200,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
@@ -24356,28 +24818,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
@@ -24504,28 +24980,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
@@ -24652,28 +25142,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
@@ -24800,28 +25304,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ161" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
@@ -24948,28 +25466,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
@@ -25552,28 +26084,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -25700,28 +26246,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
@@ -25848,28 +26408,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS168" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU168" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV168" t="inlineStr">
@@ -25996,28 +26570,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
@@ -26600,28 +27188,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
@@ -26748,28 +27350,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
@@ -26896,28 +27512,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -27044,28 +27674,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
@@ -27648,28 +28292,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
@@ -27796,28 +28454,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
@@ -27944,28 +28616,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -28092,28 +28778,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
@@ -28240,28 +28940,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
@@ -28844,28 +29558,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS188" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ188" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
@@ -28992,28 +29720,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS189" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ189" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
@@ -29140,28 +29882,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS190" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ190" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
@@ -29288,28 +30044,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ191" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
@@ -29892,28 +30662,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS195" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
@@ -30040,28 +30824,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS196" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
@@ -30188,28 +30986,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -30336,28 +31148,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS198" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
@@ -30637,28 +31463,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
@@ -31088,28 +31928,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
@@ -31236,28 +32090,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
@@ -31384,28 +32252,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
@@ -31532,28 +32414,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
@@ -32136,28 +33032,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -32284,28 +33194,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
@@ -32432,28 +33356,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
@@ -32580,28 +33518,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ213" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
@@ -33184,28 +34136,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
@@ -33332,28 +34298,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
@@ -33480,28 +34460,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ219" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
@@ -33628,28 +34622,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
@@ -33776,28 +34784,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
@@ -34380,28 +35402,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
@@ -34528,28 +35564,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
@@ -34676,28 +35726,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ227" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
@@ -34824,28 +35888,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
@@ -35428,28 +36506,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS232" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
@@ -35576,28 +36668,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS233" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ233" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
@@ -35724,28 +36830,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS234" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
@@ -35872,28 +36992,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS235" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
@@ -36476,28 +37610,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ239" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
@@ -36624,28 +37772,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ240" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
@@ -36772,28 +37934,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
@@ -36920,28 +38096,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
@@ -37524,28 +38714,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
@@ -37672,28 +38876,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
@@ -37820,28 +39038,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
@@ -37968,28 +39200,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
@@ -38116,28 +39362,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
@@ -38720,28 +39980,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR254" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS254" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
@@ -38868,28 +40142,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR255" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS255" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
@@ -39016,28 +40304,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS256" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
@@ -39164,28 +40466,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS257" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
@@ -39768,28 +41084,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
@@ -39916,28 +41246,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS262" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
@@ -40064,28 +41408,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS263" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
@@ -40212,28 +41570,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR264" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
@@ -40513,28 +41885,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR266" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
@@ -40964,28 +42350,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
@@ -41112,28 +42512,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
@@ -41260,28 +42674,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR271" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
@@ -41408,28 +42836,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
@@ -42012,28 +43454,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR276" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS276" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
@@ -42160,28 +43616,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR277" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
@@ -42308,28 +43778,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR278" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
@@ -42456,28 +43940,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR279" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
@@ -43060,28 +44558,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR283" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS283" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
@@ -43208,28 +44720,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR284" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS284" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV284" t="inlineStr">
@@ -43356,28 +44882,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR285" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS285" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
@@ -43504,28 +45044,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR286" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS286" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
@@ -43652,28 +45206,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR287" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS287" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">
@@ -44256,28 +45824,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR291" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS291" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV291" t="inlineStr">
@@ -44404,28 +45986,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP292" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR292" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS292" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ292" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV292" t="inlineStr">
@@ -44552,28 +46148,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP293" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR293" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS293" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ293" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV293" t="inlineStr">
@@ -44700,28 +46310,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR294" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS294" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ294" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV294" t="inlineStr">
@@ -45304,28 +46928,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR298" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS298" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ298" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
@@ -45452,28 +47090,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR299" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS299" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ299" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS299" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
@@ -45600,28 +47252,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR300" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS300" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ300" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS300" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
@@ -45748,28 +47414,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR301" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS301" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ301" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS301" t="inlineStr">
+        <is>
+          <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
+        </is>
+      </c>
       <c r="AT301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">

--- a/diseases/d058/2010-2014.xlsx
+++ b/diseases/d058/2010-2014.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>0.04716078490514505</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,22 +918,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1074,11 +1044,6 @@
       <c r="R4" t="n">
         <v>0.2109881872880995</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1091,22 +1056,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1227,11 +1182,6 @@
       <c r="R5" t="n">
         <v>0.01408130007574331</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1244,22 +1194,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1377,11 +1317,6 @@
       <c r="R6" t="n">
         <v>0.02665609581595155</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1394,22 +1329,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1530,11 +1455,6 @@
       <c r="R7" t="n">
         <v>0.06028233922517129</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1547,22 +1467,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1683,11 +1593,6 @@
       <c r="R8" t="n">
         <v>0.02816260015148662</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1700,22 +1605,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1833,11 +1728,6 @@
       <c r="R9" t="n">
         <v>0.02255515799811285</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1850,22 +1740,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1986,11 +1866,6 @@
       <c r="R10" t="n">
         <v>0.03444705098581216</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2003,22 +1878,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2139,11 +2004,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2156,22 +2016,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2289,11 +2139,6 @@
       <c r="R12" t="n">
         <v>0.0328075025427096</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2306,22 +2151,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2442,11 +2277,6 @@
       <c r="R13" t="n">
         <v>0.09903527158420998</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2459,22 +2289,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2595,11 +2415,6 @@
       <c r="R14" t="n">
         <v>0.04224390022722994</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2612,22 +2427,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2745,11 +2550,6 @@
       <c r="R15" t="n">
         <v>0.05536266054082245</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2762,22 +2562,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2898,11 +2688,6 @@
       <c r="R16" t="n">
         <v>0.1248705598235691</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2915,22 +2700,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3051,11 +2826,6 @@
       <c r="R17" t="n">
         <v>0.04224390022722994</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3068,22 +2838,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3201,11 +2961,6 @@
       <c r="R18" t="n">
         <v>0.05536266054082245</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3218,22 +2973,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3354,11 +3099,6 @@
       <c r="R19" t="n">
         <v>0.1507058480629282</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3371,22 +3111,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3507,11 +3237,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3524,22 +3249,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3657,11 +3372,6 @@
       <c r="R21" t="n">
         <v>0.05536266054082245</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3674,22 +3384,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3810,11 +3510,6 @@
       <c r="R22" t="n">
         <v>0.2971058147526299</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3827,22 +3522,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3963,11 +3648,6 @@
       <c r="R23" t="n">
         <v>0.05632520030297325</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3980,22 +3660,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4113,11 +3783,6 @@
       <c r="R24" t="n">
         <v>0.05536266054082245</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4130,22 +3795,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4266,11 +3921,6 @@
       <c r="R25" t="n">
         <v>0.116258797077116</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4283,22 +3933,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4419,11 +4059,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4436,22 +4071,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4569,11 +4194,6 @@
       <c r="R27" t="n">
         <v>0.123028134535161</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4586,22 +4206,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4722,11 +4332,6 @@
       <c r="R28" t="n">
         <v>0.1248705598235691</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4739,22 +4344,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4875,11 +4470,6 @@
       <c r="R29" t="n">
         <v>0.01408130007574331</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4892,22 +4482,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5025,11 +4605,6 @@
       <c r="R30" t="n">
         <v>2.466714097429978</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5042,22 +4617,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5178,11 +4743,6 @@
       <c r="R31" t="n">
         <v>0.2755764078864973</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5195,22 +4755,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5331,11 +4881,6 @@
       <c r="R32" t="n">
         <v>0.04224390022722994</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5348,22 +4893,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5481,11 +5016,6 @@
       <c r="R33" t="n">
         <v>7.857396858978949</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5498,22 +5028,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5634,11 +5154,6 @@
       <c r="R34" t="n">
         <v>0.1593176108093813</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5651,22 +5166,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5787,11 +5292,6 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5804,22 +5304,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5937,11 +5427,6 @@
       <c r="R36" t="n">
         <v>0.8304399081123368</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5954,22 +5439,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6090,11 +5565,6 @@
       <c r="R37" t="n">
         <v>0.1722352549290608</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6107,22 +5577,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6243,11 +5703,6 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6260,22 +5715,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6393,11 +5838,6 @@
       <c r="R39" t="n">
         <v>0.07531401338230277</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6410,22 +5850,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6546,11 +5976,6 @@
       <c r="R40" t="n">
         <v>0.1160138841119695</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6563,22 +5988,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6699,11 +6114,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6716,22 +6126,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6849,11 +6249,6 @@
       <c r="R42" t="n">
         <v>0.0223906526271711</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6866,22 +6261,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7002,11 +6387,6 @@
       <c r="R43" t="n">
         <v>0.004296810522665536</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7019,22 +6399,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7155,11 +6525,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7172,22 +6537,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7305,11 +6660,6 @@
       <c r="R45" t="n">
         <v>0.02035513875197372</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7322,22 +6672,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7458,11 +6798,6 @@
       <c r="R46" t="n">
         <v>0.008593621045331071</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7475,22 +6810,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7611,11 +6936,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7628,22 +6948,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7761,11 +7071,6 @@
       <c r="R48" t="n">
         <v>0.02646168037756584</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7778,22 +7083,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7914,11 +7209,6 @@
       <c r="R49" t="n">
         <v>0.04296810522665535</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7931,22 +7221,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8067,11 +7347,6 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8084,22 +7359,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8217,11 +7482,6 @@
       <c r="R51" t="n">
         <v>0.05088784687993431</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8234,22 +7494,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8370,11 +7620,6 @@
       <c r="R52" t="n">
         <v>0.07734258940797964</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8387,22 +7632,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8523,11 +7758,6 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8540,22 +7770,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8673,11 +7893,6 @@
       <c r="R54" t="n">
         <v>0.04885233300473694</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8690,22 +7905,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8826,11 +8031,6 @@
       <c r="R55" t="n">
         <v>0.2749958734505943</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8843,22 +8043,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8979,11 +8169,6 @@
       <c r="R56" t="n">
         <v>0.01399977978346401</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8996,22 +8181,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9129,11 +8304,6 @@
       <c r="R57" t="n">
         <v>0.03663924975355271</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9146,22 +8316,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9282,11 +8442,6 @@
       <c r="R58" t="n">
         <v>0.2706990629279287</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9299,22 +8454,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9435,11 +8580,6 @@
       <c r="R59" t="n">
         <v>0.01399977978346401</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9452,22 +8592,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9585,11 +8715,6 @@
       <c r="R60" t="n">
         <v>0.05699438850552643</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9602,22 +8727,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9738,11 +8853,6 @@
       <c r="R61" t="n">
         <v>0.2105437156106112</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9755,22 +8865,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9891,11 +8991,6 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9908,22 +9003,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10041,11 +9126,6 @@
       <c r="R63" t="n">
         <v>0.1567345683901977</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10058,22 +9138,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10194,11 +9264,6 @@
       <c r="R64" t="n">
         <v>0.09023302097597626</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10211,22 +9276,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10347,11 +9402,6 @@
       <c r="R65" t="n">
         <v>0.02799955956692802</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10364,22 +9414,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10497,11 +9537,6 @@
       <c r="R66" t="n">
         <v>3.714812822235205</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10514,22 +9549,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10650,11 +9675,6 @@
       <c r="R67" t="n">
         <v>0.1160138841119695</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10667,22 +9687,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10803,11 +9813,6 @@
       <c r="R68" t="n">
         <v>0.01399977978346401</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10820,22 +9825,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10953,11 +9948,6 @@
       <c r="R69" t="n">
         <v>5.532526712786458</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10970,22 +9960,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11106,11 +10086,6 @@
       <c r="R70" t="n">
         <v>0.06445215783998304</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11123,22 +10098,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11259,11 +10224,6 @@
       <c r="R71" t="n">
         <v>0.02799955956692802</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11276,22 +10236,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11409,11 +10359,6 @@
       <c r="R72" t="n">
         <v>0.7429625644470409</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11426,22 +10371,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11562,11 +10497,6 @@
       <c r="R73" t="n">
         <v>0.1332011262026316</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11579,22 +10509,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11715,11 +10635,6 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11732,22 +10647,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11865,11 +10770,6 @@
       <c r="R75" t="n">
         <v>0.1028234523641476</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11882,22 +10782,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12018,11 +10908,6 @@
       <c r="R76" t="n">
         <v>0.1242184890140098</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12035,22 +10920,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12171,11 +11046,6 @@
       <c r="R77" t="n">
         <v>0.01388684250834703</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12188,22 +11058,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12321,11 +11181,6 @@
       <c r="R78" t="n">
         <v>0.08266199111627549</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12338,22 +11193,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12474,11 +11319,6 @@
       <c r="R79" t="n">
         <v>0.05140075407476265</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12491,22 +11331,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12627,11 +11457,6 @@
       <c r="R80" t="n">
         <v>0.02777368501669407</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12644,22 +11469,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12777,11 +11592,6 @@
       <c r="R81" t="n">
         <v>0.03024219187180811</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12794,22 +11604,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12930,11 +11730,6 @@
       <c r="R82" t="n">
         <v>0.008566792345793776</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12947,22 +11742,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13083,11 +11868,6 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13100,22 +11880,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13233,11 +12003,6 @@
       <c r="R84" t="n">
         <v>0.03427448412138252</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13250,22 +12015,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13386,11 +12141,6 @@
       <c r="R85" t="n">
         <v>0.08566792345793775</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13403,22 +12153,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13539,11 +12279,6 @@
       <c r="R86" t="n">
         <v>0.01388684250834703</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13556,22 +12291,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13689,11 +12414,6 @@
       <c r="R87" t="n">
         <v>0.04032292249574414</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13706,22 +12426,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13842,11 +12552,6 @@
       <c r="R88" t="n">
         <v>0.2141698086448444</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13859,22 +12564,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13995,11 +12690,6 @@
       <c r="R89" t="n">
         <v>0.09720789755842922</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14012,22 +12702,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14145,11 +12825,6 @@
       <c r="R90" t="n">
         <v>0.0282260457470209</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14162,22 +12837,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14298,11 +12963,6 @@
       <c r="R91" t="n">
         <v>0.3983558440794105</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14315,22 +12975,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14451,11 +13101,6 @@
       <c r="R92" t="n">
         <v>0.0416605275250411</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14468,22 +13113,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14601,11 +13236,6 @@
       <c r="R93" t="n">
         <v>0.05040365311968018</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14618,22 +13248,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14754,11 +13374,6 @@
       <c r="R94" t="n">
         <v>0.2612871665467101</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14771,22 +13386,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14907,11 +13512,6 @@
       <c r="R95" t="n">
         <v>0.05554737003338813</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14924,22 +13524,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15057,11 +13647,6 @@
       <c r="R96" t="n">
         <v>0.07258126049233946</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15074,22 +13659,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15210,11 +13785,6 @@
       <c r="R97" t="n">
         <v>0.1756192430887724</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15227,22 +13797,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15363,11 +13923,6 @@
       <c r="R98" t="n">
         <v>0.01388684250834703</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15380,22 +13935,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15513,11 +14058,6 @@
       <c r="R99" t="n">
         <v>0.2056469047282951</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15530,22 +14070,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15666,11 +14196,6 @@
       <c r="R100" t="n">
         <v>0.2698539588925039</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15683,22 +14208,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -16305,11 +14820,6 @@
       <c r="R104" t="n">
         <v>0.02777368501669407</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16322,22 +14832,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16455,11 +14955,6 @@
       <c r="R105" t="n">
         <v>7.419417739216922</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16472,22 +14967,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16608,11 +15093,6 @@
       <c r="R106" t="n">
         <v>0.1927528277803599</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16625,22 +15105,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -17409,11 +15879,6 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17426,22 +15891,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17559,11 +16014,6 @@
       <c r="R112" t="n">
         <v>8.752090327701266</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17576,22 +16026,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -17712,11 +16152,6 @@
       <c r="R113" t="n">
         <v>0.1113683004953191</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17729,22 +16164,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -18675,11 +17100,6 @@
       <c r="R119" t="n">
         <v>0.02777368501669407</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18692,22 +17112,12 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -18825,11 +17235,6 @@
       <c r="R120" t="n">
         <v>0.5282302846942483</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18842,22 +17247,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -18978,11 +17373,6 @@
       <c r="R121" t="n">
         <v>0.1285018851869066</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18995,22 +17385,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -19779,11 +18159,6 @@
       <c r="R126" t="n">
         <v>0.02753176994177719</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19796,22 +18171,12 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -19929,11 +18294,6 @@
       <c r="R127" t="n">
         <v>0.0499289366437643</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19946,22 +18306,12 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -20082,11 +18432,6 @@
       <c r="R128" t="n">
         <v>0.1537352903351812</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20099,22 +18444,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20883,11 +19218,6 @@
       <c r="R133" t="n">
         <v>0.02753176994177719</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20900,22 +19230,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -21195,11 +19515,6 @@
       <c r="R135" t="n">
         <v>0.03195451945200915</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21212,22 +19527,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21348,11 +19653,6 @@
       <c r="R136" t="n">
         <v>0.03843382258379529</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21365,22 +19665,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21987,11 +20277,6 @@
       <c r="R140" t="n">
         <v>0.08259530982533157</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22004,22 +20289,12 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -22299,11 +20574,6 @@
       <c r="R142" t="n">
         <v>0.01198294479450343</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22316,22 +20586,12 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22452,11 +20712,6 @@
       <c r="R143" t="n">
         <v>0.02989297312072967</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22469,22 +20724,12 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -23253,11 +21498,6 @@
       <c r="R148" t="n">
         <v>0</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23270,22 +21510,12 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -23403,11 +21633,6 @@
       <c r="R149" t="n">
         <v>0.01797441719175515</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23420,22 +21645,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -23556,11 +21771,6 @@
       <c r="R150" t="n">
         <v>0.089678919362189</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23573,22 +21783,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -24357,11 +22557,6 @@
       <c r="R155" t="n">
         <v>0</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24374,22 +22569,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -24507,11 +22692,6 @@
       <c r="R156" t="n">
         <v>0.05991472397251715</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24524,22 +22704,12 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -24660,11 +22830,6 @@
       <c r="R157" t="n">
         <v>0.1494648656036483</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24677,22 +22842,12 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -25623,11 +23778,6 @@
       <c r="R163" t="n">
         <v>0.06882942485444297</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25640,22 +23790,12 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -25773,11 +23913,6 @@
       <c r="R164" t="n">
         <v>0.06191188143826773</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25790,22 +23925,12 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -25926,11 +24051,6 @@
       <c r="R165" t="n">
         <v>0.358715677448756</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25943,22 +24063,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -26727,11 +24837,6 @@
       <c r="R170" t="n">
         <v>0.05506353988355438</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26744,22 +24849,12 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -26877,11 +24972,6 @@
       <c r="R171" t="n">
         <v>0.0778891411642723</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26894,22 +24984,12 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -27030,11 +25110,6 @@
       <c r="R172" t="n">
         <v>0.4014199247640841</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27047,22 +25122,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -27831,11 +25896,6 @@
       <c r="R177" t="n">
         <v>0.0137658849708886</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27848,22 +25908,12 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -27981,11 +26031,6 @@
       <c r="R178" t="n">
         <v>0.05192609410951488</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27998,22 +26043,12 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -28134,11 +26169,6 @@
       <c r="R179" t="n">
         <v>0.3032001559388295</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28151,22 +26181,12 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -29097,11 +27117,6 @@
       <c r="R185" t="n">
         <v>0.04129765491266579</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29114,22 +27129,12 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
-      </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -29247,11 +27252,6 @@
       <c r="R186" t="n">
         <v>0.1497868099312929</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29264,22 +27264,12 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
-      </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -29400,11 +27390,6 @@
       <c r="R187" t="n">
         <v>0.2562254838919686</v>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29417,22 +27402,12 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
-      </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -30201,11 +28176,6 @@
       <c r="R192" t="n">
         <v>0.04129765491266579</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30218,22 +28188,12 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
-      </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -30351,11 +28311,6 @@
       <c r="R193" t="n">
         <v>7.30160769478409</v>
       </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30368,22 +28323,12 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
-      </c>
-      <c r="AU193" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -30504,11 +28449,6 @@
       <c r="R194" t="n">
         <v>0.3459044032541576</v>
       </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30521,22 +28461,12 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
-      </c>
-      <c r="AU194" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
@@ -31305,11 +29235,6 @@
       <c r="R199" t="n">
         <v>0.02753176994177719</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31322,22 +29247,12 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
-      </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -31617,11 +29532,6 @@
       <c r="R201" t="n">
         <v>12.06682540806496</v>
       </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31634,22 +29544,12 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
         <v>0</v>
-      </c>
-      <c r="AU201" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
@@ -31770,11 +29670,6 @@
       <c r="R202" t="n">
         <v>0.1195718924829187</v>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31787,22 +29682,12 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
         <v>0</v>
-      </c>
-      <c r="AU202" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
@@ -32571,11 +30456,6 @@
       <c r="R207" t="n">
         <v>0</v>
       </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32588,22 +30468,12 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
         <v>0</v>
-      </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -32721,11 +30591,6 @@
       <c r="R208" t="n">
         <v>0.8188345609577344</v>
       </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32738,22 +30603,12 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
         <v>0</v>
-      </c>
-      <c r="AU208" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
@@ -32874,11 +30729,6 @@
       <c r="R209" t="n">
         <v>0.1195718924829187</v>
       </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32891,22 +30741,12 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
         <v>0</v>
-      </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
@@ -33675,11 +31515,6 @@
       <c r="R214" t="n">
         <v>0</v>
       </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33692,22 +31527,12 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
         <v>0</v>
-      </c>
-      <c r="AU214" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
@@ -33825,11 +31650,6 @@
       <c r="R215" t="n">
         <v>0.06727470401578835</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33842,22 +31662,12 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
         <v>0</v>
-      </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
@@ -33978,11 +31788,6 @@
       <c r="R216" t="n">
         <v>0.08946519432234279</v>
       </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33995,22 +31800,12 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
         <v>0</v>
-      </c>
-      <c r="AU216" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
@@ -34941,11 +32736,6 @@
       <c r="R222" t="n">
         <v>0.01366213445849208</v>
       </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34958,22 +32748,12 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
         <v>0</v>
-      </c>
-      <c r="AU222" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
@@ -35091,11 +32871,6 @@
       <c r="R223" t="n">
         <v>0.02374401318204294</v>
       </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35108,22 +32883,12 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
-      </c>
-      <c r="AU223" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
@@ -35244,11 +33009,6 @@
       <c r="R224" t="n">
         <v>0.01704098939473196</v>
       </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35261,22 +33021,12 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
-      </c>
-      <c r="AU224" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
@@ -36045,11 +33795,6 @@
       <c r="R229" t="n">
         <v>0.02732426891698416</v>
       </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36062,22 +33807,12 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr"/>
       <c r="AT229" t="n">
         <v>0</v>
-      </c>
-      <c r="AU229" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
@@ -36195,11 +33930,6 @@
       <c r="R230" t="n">
         <v>0.03759468753823466</v>
       </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36212,22 +33942,12 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
-      </c>
-      <c r="AU230" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
@@ -36348,11 +34068,6 @@
       <c r="R231" t="n">
         <v>0.00426024734868299</v>
       </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36365,22 +34080,12 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
         <v>0</v>
-      </c>
-      <c r="AU231" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
@@ -37149,11 +34854,6 @@
       <c r="R236" t="n">
         <v>0</v>
       </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37166,22 +34866,12 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
         <v>0</v>
-      </c>
-      <c r="AU236" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
@@ -37299,11 +34989,6 @@
       <c r="R237" t="n">
         <v>0.05342402965959663</v>
       </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37316,22 +35001,12 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
         <v>0</v>
-      </c>
-      <c r="AU237" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
@@ -37452,11 +35127,6 @@
       <c r="R238" t="n">
         <v>0.03834222613814692</v>
       </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37469,22 +35139,12 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
         <v>0</v>
-      </c>
-      <c r="AU238" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
@@ -38253,11 +35913,6 @@
       <c r="R243" t="n">
         <v>0</v>
       </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38270,22 +35925,12 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
         <v>0</v>
-      </c>
-      <c r="AU243" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
@@ -38403,11 +36048,6 @@
       <c r="R244" t="n">
         <v>0.08904004943266104</v>
       </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38420,22 +36060,12 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
         <v>0</v>
-      </c>
-      <c r="AU244" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
@@ -38556,11 +36186,6 @@
       <c r="R245" t="n">
         <v>0.2470943462236134</v>
       </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38573,22 +36198,12 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
         <v>0</v>
-      </c>
-      <c r="AU245" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
@@ -39519,11 +37134,6 @@
       <c r="R251" t="n">
         <v>0.05464853783396832</v>
       </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39536,22 +37146,12 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
         <v>0</v>
-      </c>
-      <c r="AU251" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
@@ -39669,11 +37269,6 @@
       <c r="R252" t="n">
         <v>0.05342402965959663</v>
       </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39686,22 +37281,12 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
         <v>0</v>
-      </c>
-      <c r="AU252" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
@@ -39822,11 +37407,6 @@
       <c r="R253" t="n">
         <v>0.3749017666841032</v>
       </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39839,22 +37419,12 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr"/>
       <c r="AT253" t="n">
         <v>0</v>
-      </c>
-      <c r="AU253" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
@@ -40623,11 +38193,6 @@
       <c r="R258" t="n">
         <v>0.08197280675095248</v>
       </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40640,22 +38205,12 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
         <v>0</v>
-      </c>
-      <c r="AU258" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
@@ -40773,11 +38328,6 @@
       <c r="R259" t="n">
         <v>0.07321070731129908</v>
       </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40790,22 +38340,12 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
         <v>0</v>
-      </c>
-      <c r="AU259" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
@@ -40926,11 +38466,6 @@
       <c r="R260" t="n">
         <v>0.3109980564538583</v>
       </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40943,22 +38478,12 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
         <v>0</v>
-      </c>
-      <c r="AU260" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
@@ -41727,11 +39252,6 @@
       <c r="R265" t="n">
         <v>0.01366213445849208</v>
       </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41744,22 +39264,12 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
         <v>0</v>
-      </c>
-      <c r="AU265" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
@@ -42039,11 +39549,6 @@
       <c r="R267" t="n">
         <v>0.09299738496300154</v>
       </c>
-      <c r="S267" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42056,22 +39561,12 @@
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
         <v>0</v>
-      </c>
-      <c r="AU267" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
@@ -42192,11 +39687,6 @@
       <c r="R268" t="n">
         <v>0.1150266784144408</v>
       </c>
-      <c r="S268" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42209,22 +39699,12 @@
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR268" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
         <v>0</v>
-      </c>
-      <c r="AU268" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
@@ -42993,11 +40473,6 @@
       <c r="R273" t="n">
         <v>0.02732426891698416</v>
       </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43010,22 +40485,12 @@
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
         <v>0</v>
-      </c>
-      <c r="AU273" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
@@ -43143,11 +40608,6 @@
       <c r="R274" t="n">
         <v>0.5124749511790936</v>
       </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA274" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43160,22 +40620,12 @@
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR274" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS274" t="inlineStr"/>
       <c r="AT274" t="n">
         <v>0</v>
-      </c>
-      <c r="AU274" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
@@ -43296,11 +40746,6 @@
       <c r="R275" t="n">
         <v>0.2215328621315155</v>
       </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43313,22 +40758,12 @@
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR275" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS275" t="inlineStr"/>
       <c r="AT275" t="n">
         <v>0</v>
-      </c>
-      <c r="AU275" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
@@ -44097,11 +41532,6 @@
       <c r="R280" t="n">
         <v>0.01366213445849208</v>
       </c>
-      <c r="S280" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44114,22 +41544,12 @@
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR280" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS280" t="inlineStr"/>
       <c r="AT280" t="n">
         <v>0</v>
-      </c>
-      <c r="AU280" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
@@ -44247,11 +41667,6 @@
       <c r="R281" t="n">
         <v>8.045263133182218</v>
       </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44264,22 +41679,12 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR281" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS281" t="inlineStr"/>
       <c r="AT281" t="n">
         <v>0</v>
-      </c>
-      <c r="AU281" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
@@ -44400,11 +41805,6 @@
       <c r="R282" t="n">
         <v>0.1448484098552217</v>
       </c>
-      <c r="S282" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA282" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44417,22 +41817,12 @@
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR282" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS282" t="inlineStr"/>
       <c r="AT282" t="n">
         <v>0</v>
-      </c>
-      <c r="AU282" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
@@ -45363,11 +42753,6 @@
       <c r="R288" t="n">
         <v>0.02732426891698416</v>
       </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45380,22 +42765,12 @@
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR288" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS288" t="inlineStr"/>
       <c r="AT288" t="n">
         <v>0</v>
-      </c>
-      <c r="AU288" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
@@ -45513,11 +42888,6 @@
       <c r="R289" t="n">
         <v>6.533560960592149</v>
       </c>
-      <c r="S289" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA289" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45530,22 +42900,12 @@
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR289" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS289" t="inlineStr"/>
       <c r="AT289" t="n">
         <v>0</v>
-      </c>
-      <c r="AU289" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV289" t="inlineStr">
         <is>
@@ -45666,11 +43026,6 @@
       <c r="R290" t="n">
         <v>0.07668445227629384</v>
       </c>
-      <c r="S290" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA290" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45683,22 +43038,12 @@
       </c>
       <c r="AP290" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR290" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS290" t="inlineStr"/>
       <c r="AT290" t="n">
         <v>0</v>
-      </c>
-      <c r="AU290" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV290" t="inlineStr">
         <is>
@@ -46467,11 +43812,6 @@
       <c r="R295" t="n">
         <v>0</v>
       </c>
-      <c r="S295" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA295" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46484,22 +43824,12 @@
       </c>
       <c r="AP295" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR295" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS295" t="inlineStr"/>
       <c r="AT295" t="n">
         <v>0</v>
-      </c>
-      <c r="AU295" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV295" t="inlineStr">
         <is>
@@ -46617,11 +43947,6 @@
       <c r="R296" t="n">
         <v>0.5045602801184126</v>
       </c>
-      <c r="S296" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA296" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46634,22 +43959,12 @@
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR296" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS296" t="inlineStr"/>
       <c r="AT296" t="n">
         <v>0</v>
-      </c>
-      <c r="AU296" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV296" t="inlineStr">
         <is>
@@ -46770,11 +44085,6 @@
       <c r="R297" t="n">
         <v>0.1405881625065387</v>
       </c>
-      <c r="S297" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA297" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46787,22 +44097,12 @@
       </c>
       <c r="AP297" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR297" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS297" t="inlineStr"/>
       <c r="AT297" t="n">
         <v>0</v>
-      </c>
-      <c r="AU297" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV297" t="inlineStr">
         <is>

--- a/diseases/d058/2010-2014.xlsx
+++ b/diseases/d058/2010-2014.xlsx
@@ -14328,17 +14328,15 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U101" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -14346,7 +14344,7 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -14356,12 +14354,7 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ101" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
@@ -14371,11 +14364,6 @@
       </c>
       <c r="AT101" t="n">
         <v>1</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -14490,17 +14478,15 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -14508,7 +14494,7 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -14518,12 +14504,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -14533,11 +14514,6 @@
       </c>
       <c r="AT102" t="n">
         <v>1</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -14652,17 +14628,15 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -14670,7 +14644,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -14680,12 +14654,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -14695,11 +14664,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -15225,17 +15189,15 @@
       <c r="O107" t="n">
         <v>2</v>
       </c>
+      <c r="P107" t="n">
+        <v>2</v>
+      </c>
       <c r="Q107" t="n">
         <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>0.001563375917999682</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U107" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -15243,7 +15205,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -15253,12 +15215,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
@@ -15268,11 +15225,6 @@
       </c>
       <c r="AT107" t="n">
         <v>1</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15387,17 +15339,15 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -15405,7 +15355,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -15415,12 +15365,7 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ108" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
@@ -15430,11 +15375,6 @@
       </c>
       <c r="AT108" t="n">
         <v>1</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -15549,17 +15489,15 @@
       <c r="O109" t="n">
         <v>5</v>
       </c>
+      <c r="P109" t="n">
+        <v>5</v>
+      </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
         <v>0.003908439794999206</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U109" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -15567,7 +15505,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -15577,12 +15515,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ109" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
@@ -15592,11 +15525,6 @@
       </c>
       <c r="AT109" t="n">
         <v>1</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -15711,17 +15639,15 @@
       <c r="O110" t="n">
         <v>3</v>
       </c>
+      <c r="P110" t="n">
+        <v>3</v>
+      </c>
       <c r="Q110" t="n">
         <v>0</v>
       </c>
       <c r="R110" t="n">
         <v>0.002345063876999524</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U110" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -15729,7 +15655,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -15739,12 +15665,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
@@ -15754,11 +15675,6 @@
       </c>
       <c r="AT110" t="n">
         <v>1</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -16284,17 +16200,15 @@
       <c r="O114" t="n">
         <v>4</v>
       </c>
+      <c r="P114" t="n">
+        <v>4</v>
+      </c>
       <c r="Q114" t="n">
         <v>0</v>
       </c>
       <c r="R114" t="n">
         <v>0.003126751835999364</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -16302,7 +16216,7 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -16312,12 +16226,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -16327,11 +16236,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -16446,17 +16350,15 @@
       <c r="O115" t="n">
         <v>21</v>
       </c>
+      <c r="P115" t="n">
+        <v>21</v>
+      </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
         <v>0.01641544713899666</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -16464,7 +16366,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -16474,12 +16376,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -16489,11 +16386,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -16608,17 +16500,15 @@
       <c r="O116" t="n">
         <v>16</v>
       </c>
+      <c r="P116" t="n">
+        <v>16</v>
+      </c>
       <c r="Q116" t="n">
         <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>0.01250700734399746</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -16626,7 +16516,7 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -16636,12 +16526,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -16651,11 +16536,6 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -16770,17 +16650,15 @@
       <c r="O117" t="n">
         <v>23</v>
       </c>
+      <c r="P117" t="n">
+        <v>23</v>
+      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0.01797882305699635</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -16788,7 +16666,7 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -16798,12 +16676,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
@@ -16813,11 +16686,6 @@
       </c>
       <c r="AT117" t="n">
         <v>1</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -16932,17 +16800,15 @@
       <c r="O118" t="n">
         <v>24</v>
       </c>
+      <c r="P118" t="n">
+        <v>24</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0.01876051101599619</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -16950,7 +16816,7 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -16960,12 +16826,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
@@ -16975,11 +16836,6 @@
       </c>
       <c r="AT118" t="n">
         <v>1</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -17505,17 +17361,15 @@
       <c r="O122" t="n">
         <v>30</v>
       </c>
+      <c r="P122" t="n">
+        <v>30</v>
+      </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
         <v>0.02345063876999524</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -17523,7 +17377,7 @@
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -17533,12 +17387,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
@@ -17548,11 +17397,6 @@
       </c>
       <c r="AT122" t="n">
         <v>1</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -17667,17 +17511,15 @@
       <c r="O123" t="n">
         <v>21</v>
       </c>
+      <c r="P123" t="n">
+        <v>21</v>
+      </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>0.01641544713899666</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U123" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -17685,7 +17527,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -17695,12 +17537,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
@@ -17710,11 +17547,6 @@
       </c>
       <c r="AT123" t="n">
         <v>1</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -17829,17 +17661,15 @@
       <c r="O124" t="n">
         <v>11</v>
       </c>
+      <c r="P124" t="n">
+        <v>11</v>
+      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>0.008598567548998253</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -17847,7 +17677,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -17857,12 +17687,7 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
@@ -17872,11 +17697,6 @@
       </c>
       <c r="AT124" t="n">
         <v>1</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -17991,17 +17811,15 @@
       <c r="O125" t="n">
         <v>14</v>
       </c>
+      <c r="P125" t="n">
+        <v>14</v>
+      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0.01094363142599778</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -18009,7 +17827,7 @@
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -18019,12 +17837,7 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ125" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
@@ -18034,11 +17847,6 @@
       </c>
       <c r="AT125" t="n">
         <v>1</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -18564,17 +18372,15 @@
       <c r="O129" t="n">
         <v>2</v>
       </c>
+      <c r="P129" t="n">
+        <v>2</v>
+      </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U129" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -18582,7 +18388,7 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -18592,12 +18398,7 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ129" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
@@ -18607,11 +18408,6 @@
       </c>
       <c r="AT129" t="n">
         <v>1</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -18726,17 +18522,15 @@
       <c r="O130" t="n">
         <v>10</v>
       </c>
+      <c r="P130" t="n">
+        <v>10</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0.007829403835799534</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U130" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -18744,7 +18538,7 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -18754,12 +18548,7 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ130" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
@@ -18769,11 +18558,6 @@
       </c>
       <c r="AT130" t="n">
         <v>1</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -18888,17 +18672,15 @@
       <c r="O131" t="n">
         <v>3</v>
       </c>
+      <c r="P131" t="n">
+        <v>3</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U131" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -18906,7 +18688,7 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -18916,12 +18698,7 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
@@ -18931,11 +18708,6 @@
       </c>
       <c r="AT131" t="n">
         <v>1</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -19050,17 +18822,15 @@
       <c r="O132" t="n">
         <v>3</v>
       </c>
+      <c r="P132" t="n">
+        <v>3</v>
+      </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U132" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -19068,7 +18838,7 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -19078,12 +18848,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
@@ -19093,11 +18858,6 @@
       </c>
       <c r="AT132" t="n">
         <v>1</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -19350,17 +19110,15 @@
       <c r="O134" t="n">
         <v>7</v>
       </c>
+      <c r="P134" t="n">
+        <v>7</v>
+      </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>0.005480582685059674</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U134" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -19368,7 +19126,7 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -19378,12 +19136,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
@@ -19393,11 +19146,6 @@
       </c>
       <c r="AT134" t="n">
         <v>1</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -19785,17 +19533,15 @@
       <c r="O137" t="n">
         <v>3</v>
       </c>
+      <c r="P137" t="n">
+        <v>3</v>
+      </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -19803,7 +19549,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -19813,12 +19559,7 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
@@ -19828,11 +19569,6 @@
       </c>
       <c r="AT137" t="n">
         <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -19947,17 +19683,15 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -19965,7 +19699,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -19975,12 +19709,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
@@ -19990,11 +19719,6 @@
       </c>
       <c r="AT138" t="n">
         <v>1</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -20109,17 +19833,15 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
+      <c r="P139" t="n">
+        <v>1</v>
+      </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U139" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -20127,7 +19849,7 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -20137,12 +19859,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ139" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
@@ -20152,11 +19869,6 @@
       </c>
       <c r="AT139" t="n">
         <v>1</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -20409,17 +20121,15 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
+      <c r="P141" t="n">
+        <v>0</v>
+      </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -20427,7 +20137,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -20437,12 +20147,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ141" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
@@ -20452,11 +20157,6 @@
       </c>
       <c r="AT141" t="n">
         <v>1</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -20844,17 +20544,15 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -20862,7 +20560,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -20872,12 +20570,7 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
@@ -20887,11 +20580,6 @@
       </c>
       <c r="AT144" t="n">
         <v>1</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -21006,17 +20694,15 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
+      <c r="P145" t="n">
+        <v>1</v>
+      </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -21024,7 +20710,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -21034,12 +20720,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ145" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
@@ -21049,11 +20730,6 @@
       </c>
       <c r="AT145" t="n">
         <v>1</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -21168,17 +20844,15 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U146" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -21186,7 +20860,7 @@
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -21196,12 +20870,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
@@ -21211,11 +20880,6 @@
       </c>
       <c r="AT146" t="n">
         <v>1</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -21330,17 +20994,15 @@
       <c r="O147" t="n">
         <v>0</v>
       </c>
+      <c r="P147" t="n">
+        <v>0</v>
+      </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>0</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -21348,7 +21010,7 @@
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -21358,12 +21020,7 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
@@ -21373,11 +21030,6 @@
       </c>
       <c r="AT147" t="n">
         <v>1</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -21903,17 +21555,15 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U151" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -21921,7 +21571,7 @@
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -21931,12 +21581,7 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
@@ -21946,11 +21591,6 @@
       </c>
       <c r="AT151" t="n">
         <v>1</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -22065,17 +21705,15 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U152" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -22083,7 +21721,7 @@
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -22093,12 +21731,7 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
@@ -22108,11 +21741,6 @@
       </c>
       <c r="AT152" t="n">
         <v>1</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -22227,17 +21855,15 @@
       <c r="O153" t="n">
         <v>2</v>
       </c>
+      <c r="P153" t="n">
+        <v>2</v>
+      </c>
       <c r="Q153" t="n">
         <v>0</v>
       </c>
       <c r="R153" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U153" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -22245,7 +21871,7 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -22255,12 +21881,7 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
@@ -22270,11 +21891,6 @@
       </c>
       <c r="AT153" t="n">
         <v>1</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -22389,17 +22005,15 @@
       <c r="O154" t="n">
         <v>2</v>
       </c>
+      <c r="P154" t="n">
+        <v>2</v>
+      </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -22407,7 +22021,7 @@
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -22417,12 +22031,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
@@ -22432,11 +22041,6 @@
       </c>
       <c r="AT154" t="n">
         <v>1</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -22962,17 +22566,15 @@
       <c r="O158" t="n">
         <v>4</v>
       </c>
+      <c r="P158" t="n">
+        <v>4</v>
+      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0.003131761534319814</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U158" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -22980,7 +22582,7 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -22990,12 +22592,7 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
@@ -23005,11 +22602,6 @@
       </c>
       <c r="AT158" t="n">
         <v>1</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -23124,17 +22716,15 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
+      <c r="P159" t="n">
+        <v>1</v>
+      </c>
       <c r="Q159" t="n">
         <v>0</v>
       </c>
       <c r="R159" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -23142,7 +22732,7 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -23152,12 +22742,7 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
@@ -23167,11 +22752,6 @@
       </c>
       <c r="AT159" t="n">
         <v>1</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -23286,17 +22866,15 @@
       <c r="O160" t="n">
         <v>7</v>
       </c>
+      <c r="P160" t="n">
+        <v>7</v>
+      </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>0.005480582685059674</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U160" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -23304,7 +22882,7 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -23314,12 +22892,7 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
@@ -23329,11 +22902,6 @@
       </c>
       <c r="AT160" t="n">
         <v>1</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -23448,17 +23016,15 @@
       <c r="O161" t="n">
         <v>6</v>
       </c>
+      <c r="P161" t="n">
+        <v>6</v>
+      </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
         <v>0.004697642301479722</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U161" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -23466,7 +23032,7 @@
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -23476,12 +23042,7 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
@@ -23491,11 +23052,6 @@
       </c>
       <c r="AT161" t="n">
         <v>1</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -23610,17 +23166,15 @@
       <c r="O162" t="n">
         <v>11</v>
       </c>
+      <c r="P162" t="n">
+        <v>11</v>
+      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0.008612344219379489</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U162" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -23628,7 +23182,7 @@
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -23638,12 +23192,7 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
@@ -23653,11 +23202,6 @@
       </c>
       <c r="AT162" t="n">
         <v>1</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -24183,17 +23727,15 @@
       <c r="O166" t="n">
         <v>6</v>
       </c>
+      <c r="P166" t="n">
+        <v>6</v>
+      </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
         <v>0.004697642301479722</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U166" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -24201,7 +23743,7 @@
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -24211,12 +23753,7 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ166" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
@@ -24226,11 +23763,6 @@
       </c>
       <c r="AT166" t="n">
         <v>1</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -24345,17 +23877,15 @@
       <c r="O167" t="n">
         <v>17</v>
       </c>
+      <c r="P167" t="n">
+        <v>17</v>
+      </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>0.01330998652085921</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U167" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -24363,7 +23893,7 @@
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -24373,12 +23903,7 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
@@ -24388,11 +23913,6 @@
       </c>
       <c r="AT167" t="n">
         <v>1</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -24507,17 +24027,15 @@
       <c r="O168" t="n">
         <v>5</v>
       </c>
+      <c r="P168" t="n">
+        <v>5</v>
+      </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
         <v>0.003914701917899767</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U168" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -24525,7 +24043,7 @@
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -24535,12 +24053,7 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ168" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr">
@@ -24550,11 +24063,6 @@
       </c>
       <c r="AT168" t="n">
         <v>1</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -24669,17 +24177,15 @@
       <c r="O169" t="n">
         <v>8</v>
       </c>
+      <c r="P169" t="n">
+        <v>8</v>
+      </c>
       <c r="Q169" t="n">
         <v>0</v>
       </c>
       <c r="R169" t="n">
         <v>0.006263523068639628</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U169" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -24687,7 +24193,7 @@
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -24697,12 +24203,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr">
@@ -24712,11 +24213,6 @@
       </c>
       <c r="AT169" t="n">
         <v>1</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -25242,17 +24738,15 @@
       <c r="O173" t="n">
         <v>6</v>
       </c>
+      <c r="P173" t="n">
+        <v>6</v>
+      </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>0.004697642301479722</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U173" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -25260,7 +24754,7 @@
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -25270,12 +24764,7 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ173" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
@@ -25285,11 +24774,6 @@
       </c>
       <c r="AT173" t="n">
         <v>1</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -25404,17 +24888,15 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
+      <c r="P174" t="n">
+        <v>1</v>
+      </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U174" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -25422,7 +24904,7 @@
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -25432,12 +24914,7 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
@@ -25447,11 +24924,6 @@
       </c>
       <c r="AT174" t="n">
         <v>1</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -25566,17 +25038,15 @@
       <c r="O175" t="n">
         <v>4</v>
       </c>
+      <c r="P175" t="n">
+        <v>4</v>
+      </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
         <v>0.003131761534319814</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -25584,7 +25054,7 @@
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -25594,12 +25064,7 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ175" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
@@ -25609,11 +25074,6 @@
       </c>
       <c r="AT175" t="n">
         <v>1</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -25728,17 +25188,15 @@
       <c r="O176" t="n">
         <v>3</v>
       </c>
+      <c r="P176" t="n">
+        <v>3</v>
+      </c>
       <c r="Q176" t="n">
         <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0.002348821150739861</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U176" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -25746,7 +25204,7 @@
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -25756,12 +25214,7 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
@@ -25771,11 +25224,6 @@
       </c>
       <c r="AT176" t="n">
         <v>1</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -26301,17 +25749,15 @@
       <c r="O180" t="n">
         <v>2</v>
       </c>
+      <c r="P180" t="n">
+        <v>2</v>
+      </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
         <v>0.001565880767159907</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U180" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -26319,7 +25765,7 @@
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -26329,12 +25775,7 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
@@ -26344,11 +25785,6 @@
       </c>
       <c r="AT180" t="n">
         <v>1</v>
-      </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -26463,17 +25899,15 @@
       <c r="O181" t="n">
         <v>1</v>
       </c>
+      <c r="P181" t="n">
+        <v>1</v>
+      </c>
       <c r="Q181" t="n">
         <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U181" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -26481,7 +25915,7 @@
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -26491,12 +25925,7 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
@@ -26506,11 +25935,6 @@
       </c>
       <c r="AT181" t="n">
         <v>1</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
@@ -26625,17 +26049,15 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
       <c r="Q182" t="n">
         <v>0</v>
       </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U182" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -26643,7 +26065,7 @@
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -26653,12 +26075,7 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
@@ -26668,11 +26085,6 @@
       </c>
       <c r="AT182" t="n">
         <v>1</v>
-      </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
@@ -26787,17 +26199,15 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
       <c r="Q183" t="n">
         <v>0</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -26805,7 +26215,7 @@
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -26815,12 +26225,7 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
@@ -26830,11 +26235,6 @@
       </c>
       <c r="AT183" t="n">
         <v>1</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -26949,17 +26349,15 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
       <c r="Q184" t="n">
         <v>0</v>
       </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U184" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -26967,7 +26365,7 @@
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -26977,12 +26375,7 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
@@ -26992,11 +26385,6 @@
       </c>
       <c r="AT184" t="n">
         <v>1</v>
-      </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -27522,17 +26910,15 @@
       <c r="O188" t="n">
         <v>1</v>
       </c>
+      <c r="P188" t="n">
+        <v>1</v>
+      </c>
       <c r="Q188" t="n">
         <v>0</v>
       </c>
       <c r="R188" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U188" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -27540,7 +26926,7 @@
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -27550,12 +26936,7 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ188" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr">
@@ -27565,11 +26946,6 @@
       </c>
       <c r="AT188" t="n">
         <v>1</v>
-      </c>
-      <c r="AU188" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -27684,17 +27060,15 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
       <c r="Q189" t="n">
         <v>0</v>
       </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U189" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -27702,7 +27076,7 @@
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -27712,12 +27086,7 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ189" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
@@ -27727,11 +27096,6 @@
       </c>
       <c r="AT189" t="n">
         <v>1</v>
-      </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -27846,17 +27210,15 @@
       <c r="O190" t="n">
         <v>0</v>
       </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
       <c r="Q190" t="n">
         <v>0</v>
       </c>
       <c r="R190" t="n">
         <v>0</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U190" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -27864,7 +27226,7 @@
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -27874,12 +27236,7 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ190" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
@@ -27889,11 +27246,6 @@
       </c>
       <c r="AT190" t="n">
         <v>1</v>
-      </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -28008,17 +27360,15 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
+      <c r="P191" t="n">
+        <v>1</v>
+      </c>
       <c r="Q191" t="n">
         <v>0</v>
       </c>
       <c r="R191" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U191" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -28026,7 +27376,7 @@
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -28036,12 +27386,7 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
@@ -28051,11 +27396,6 @@
       </c>
       <c r="AT191" t="n">
         <v>1</v>
-      </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
@@ -28581,17 +27921,15 @@
       <c r="O195" t="n">
         <v>0</v>
       </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
       <c r="Q195" t="n">
         <v>0</v>
       </c>
       <c r="R195" t="n">
         <v>0</v>
       </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U195" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -28599,7 +27937,7 @@
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -28609,12 +27947,7 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ195" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
@@ -28624,11 +27957,6 @@
       </c>
       <c r="AT195" t="n">
         <v>1</v>
-      </c>
-      <c r="AU195" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
@@ -28743,17 +28071,15 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
+      <c r="P196" t="n">
+        <v>1</v>
+      </c>
       <c r="Q196" t="n">
         <v>0</v>
       </c>
       <c r="R196" t="n">
         <v>0.0007829403835799535</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -28761,7 +28087,7 @@
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -28771,12 +28097,7 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ196" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
@@ -28786,11 +28107,6 @@
       </c>
       <c r="AT196" t="n">
         <v>1</v>
-      </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
@@ -28905,17 +28221,15 @@
       <c r="O197" t="n">
         <v>5</v>
       </c>
+      <c r="P197" t="n">
+        <v>5</v>
+      </c>
       <c r="Q197" t="n">
         <v>0</v>
       </c>
       <c r="R197" t="n">
         <v>0.003914701917899767</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U197" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -28923,7 +28237,7 @@
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -28933,12 +28247,7 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr">
@@ -28948,11 +28257,6 @@
       </c>
       <c r="AT197" t="n">
         <v>1</v>
-      </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
@@ -29067,17 +28371,15 @@
       <c r="O198" t="n">
         <v>6</v>
       </c>
+      <c r="P198" t="n">
+        <v>6</v>
+      </c>
       <c r="Q198" t="n">
         <v>0</v>
       </c>
       <c r="R198" t="n">
         <v>0.004697642301479722</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U198" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -29085,7 +28387,7 @@
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -29095,12 +28397,7 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ198" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
@@ -29110,11 +28407,6 @@
       </c>
       <c r="AT198" t="n">
         <v>1</v>
-      </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
@@ -29367,17 +28659,15 @@
       <c r="O200" t="n">
         <v>4</v>
       </c>
+      <c r="P200" t="n">
+        <v>4</v>
+      </c>
       <c r="Q200" t="n">
         <v>0</v>
       </c>
       <c r="R200" t="n">
         <v>0.003131761534319814</v>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U200" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -29385,7 +28675,7 @@
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -29395,12 +28685,7 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
@@ -29410,11 +28695,6 @@
       </c>
       <c r="AT200" t="n">
         <v>1</v>
-      </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
@@ -29802,17 +29082,15 @@
       <c r="O203" t="n">
         <v>8</v>
       </c>
+      <c r="P203" t="n">
+        <v>8</v>
+      </c>
       <c r="Q203" t="n">
         <v>0</v>
       </c>
       <c r="R203" t="n">
         <v>0.006263523068639628</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U203" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -29820,7 +29098,7 @@
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -29830,12 +29108,7 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
@@ -29845,11 +29118,6 @@
       </c>
       <c r="AT203" t="n">
         <v>1</v>
-      </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
@@ -29964,17 +29232,15 @@
       <c r="O204" t="n">
         <v>26</v>
       </c>
+      <c r="P204" t="n">
+        <v>26</v>
+      </c>
       <c r="Q204" t="n">
         <v>0</v>
       </c>
       <c r="R204" t="n">
         <v>0.02035644997307879</v>
       </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U204" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -29982,7 +29248,7 @@
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -29992,12 +29258,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
@@ -30007,11 +29268,6 @@
       </c>
       <c r="AT204" t="n">
         <v>1</v>
-      </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
@@ -30126,17 +29382,15 @@
       <c r="O205" t="n">
         <v>18</v>
       </c>
+      <c r="P205" t="n">
+        <v>18</v>
+      </c>
       <c r="Q205" t="n">
         <v>0</v>
       </c>
       <c r="R205" t="n">
         <v>0.01409292690443916</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U205" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -30144,7 +29398,7 @@
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -30154,12 +29408,7 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ205" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr">
@@ -30169,11 +29418,6 @@
       </c>
       <c r="AT205" t="n">
         <v>1</v>
-      </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
@@ -30288,17 +29532,15 @@
       <c r="O206" t="n">
         <v>20</v>
       </c>
+      <c r="P206" t="n">
+        <v>20</v>
+      </c>
       <c r="Q206" t="n">
         <v>0</v>
       </c>
       <c r="R206" t="n">
         <v>0.01565880767159907</v>
       </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U206" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -30306,7 +29548,7 @@
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -30316,12 +29558,7 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ206" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr">
@@ -30331,11 +29568,6 @@
       </c>
       <c r="AT206" t="n">
         <v>1</v>
-      </c>
-      <c r="AU206" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
@@ -30861,17 +30093,15 @@
       <c r="O210" t="n">
         <v>22</v>
       </c>
+      <c r="P210" t="n">
+        <v>22</v>
+      </c>
       <c r="Q210" t="n">
         <v>0</v>
       </c>
       <c r="R210" t="n">
         <v>0.01722468843875898</v>
       </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U210" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -30879,7 +30109,7 @@
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -30889,12 +30119,7 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ210" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
@@ -30904,11 +30129,6 @@
       </c>
       <c r="AT210" t="n">
         <v>1</v>
-      </c>
-      <c r="AU210" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
@@ -31023,17 +30243,15 @@
       <c r="O211" t="n">
         <v>22</v>
       </c>
+      <c r="P211" t="n">
+        <v>22</v>
+      </c>
       <c r="Q211" t="n">
         <v>0</v>
       </c>
       <c r="R211" t="n">
         <v>0.01722468843875898</v>
       </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U211" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -31041,7 +30259,7 @@
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -31051,12 +30269,7 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ211" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
@@ -31066,11 +30279,6 @@
       </c>
       <c r="AT211" t="n">
         <v>1</v>
-      </c>
-      <c r="AU211" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
@@ -31185,17 +30393,15 @@
       <c r="O212" t="n">
         <v>17</v>
       </c>
+      <c r="P212" t="n">
+        <v>17</v>
+      </c>
       <c r="Q212" t="n">
         <v>0</v>
       </c>
       <c r="R212" t="n">
         <v>0.01330998652085921</v>
       </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U212" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -31203,7 +30409,7 @@
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
@@ -31213,12 +30419,7 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
@@ -31228,11 +30429,6 @@
       </c>
       <c r="AT212" t="n">
         <v>1</v>
-      </c>
-      <c r="AU212" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
@@ -31347,17 +30543,15 @@
       <c r="O213" t="n">
         <v>6</v>
       </c>
+      <c r="P213" t="n">
+        <v>6</v>
+      </c>
       <c r="Q213" t="n">
         <v>0</v>
       </c>
       <c r="R213" t="n">
         <v>0.004697642301479722</v>
       </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U213" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -31365,7 +30559,7 @@
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -31375,12 +30569,7 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr">
@@ -31390,11 +30579,6 @@
       </c>
       <c r="AT213" t="n">
         <v>1</v>
-      </c>
-      <c r="AU213" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
@@ -31920,17 +31104,15 @@
       <c r="O217" t="n">
         <v>4</v>
       </c>
+      <c r="P217" t="n">
+        <v>4</v>
+      </c>
       <c r="Q217" t="n">
         <v>0</v>
       </c>
       <c r="R217" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U217" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -31938,7 +31120,7 @@
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -31948,12 +31130,7 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr">
@@ -31963,11 +31140,6 @@
       </c>
       <c r="AT217" t="n">
         <v>1</v>
-      </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
@@ -32082,17 +31254,15 @@
       <c r="O218" t="n">
         <v>7</v>
       </c>
+      <c r="P218" t="n">
+        <v>7</v>
+      </c>
       <c r="Q218" t="n">
         <v>0</v>
       </c>
       <c r="R218" t="n">
         <v>0.005490772954110641</v>
       </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U218" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -32100,7 +31270,7 @@
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -32110,12 +31280,7 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ218" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr">
@@ -32125,11 +31290,6 @@
       </c>
       <c r="AT218" t="n">
         <v>1</v>
-      </c>
-      <c r="AU218" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
@@ -32244,17 +31404,15 @@
       <c r="O219" t="n">
         <v>2</v>
       </c>
+      <c r="P219" t="n">
+        <v>2</v>
+      </c>
       <c r="Q219" t="n">
         <v>0</v>
       </c>
       <c r="R219" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U219" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -32262,7 +31420,7 @@
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -32272,12 +31430,7 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr">
@@ -32287,11 +31440,6 @@
       </c>
       <c r="AT219" t="n">
         <v>1</v>
-      </c>
-      <c r="AU219" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
@@ -32406,17 +31554,15 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
       <c r="Q220" t="n">
         <v>0</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
       </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U220" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -32424,7 +31570,7 @@
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
@@ -32434,12 +31580,7 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
@@ -32449,11 +31590,6 @@
       </c>
       <c r="AT220" t="n">
         <v>1</v>
-      </c>
-      <c r="AU220" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
@@ -32568,17 +31704,15 @@
       <c r="O221" t="n">
         <v>4</v>
       </c>
+      <c r="P221" t="n">
+        <v>4</v>
+      </c>
       <c r="Q221" t="n">
         <v>0</v>
       </c>
       <c r="R221" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U221" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -32586,7 +31720,7 @@
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -32596,12 +31730,7 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
@@ -32611,11 +31740,6 @@
       </c>
       <c r="AT221" t="n">
         <v>1</v>
-      </c>
-      <c r="AU221" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
@@ -33141,17 +32265,15 @@
       <c r="O225" t="n">
         <v>1</v>
       </c>
+      <c r="P225" t="n">
+        <v>1</v>
+      </c>
       <c r="Q225" t="n">
         <v>0</v>
       </c>
       <c r="R225" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U225" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -33159,7 +32281,7 @@
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
@@ -33169,12 +32291,7 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ225" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr">
@@ -33184,11 +32301,6 @@
       </c>
       <c r="AT225" t="n">
         <v>1</v>
-      </c>
-      <c r="AU225" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
@@ -33303,17 +32415,15 @@
       <c r="O226" t="n">
         <v>2</v>
       </c>
+      <c r="P226" t="n">
+        <v>2</v>
+      </c>
       <c r="Q226" t="n">
         <v>0</v>
       </c>
       <c r="R226" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U226" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -33321,7 +32431,7 @@
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -33331,12 +32441,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
@@ -33346,11 +32451,6 @@
       </c>
       <c r="AT226" t="n">
         <v>1</v>
-      </c>
-      <c r="AU226" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
@@ -33465,17 +32565,15 @@
       <c r="O227" t="n">
         <v>2</v>
       </c>
+      <c r="P227" t="n">
+        <v>2</v>
+      </c>
       <c r="Q227" t="n">
         <v>0</v>
       </c>
       <c r="R227" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U227" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -33483,7 +32581,7 @@
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -33493,12 +32591,7 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
@@ -33508,11 +32601,6 @@
       </c>
       <c r="AT227" t="n">
         <v>1</v>
-      </c>
-      <c r="AU227" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
@@ -33627,17 +32715,15 @@
       <c r="O228" t="n">
         <v>1</v>
       </c>
+      <c r="P228" t="n">
+        <v>1</v>
+      </c>
       <c r="Q228" t="n">
         <v>0</v>
       </c>
       <c r="R228" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U228" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -33645,7 +32731,7 @@
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -33655,12 +32741,7 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ228" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
@@ -33670,11 +32751,6 @@
       </c>
       <c r="AT228" t="n">
         <v>1</v>
-      </c>
-      <c r="AU228" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
@@ -34200,17 +33276,15 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
       <c r="Q232" t="n">
         <v>0</v>
       </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U232" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -34218,7 +33292,7 @@
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
@@ -34228,12 +33302,7 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ232" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
@@ -34243,11 +33312,6 @@
       </c>
       <c r="AT232" t="n">
         <v>1</v>
-      </c>
-      <c r="AU232" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
@@ -34362,17 +33426,15 @@
       <c r="O233" t="n">
         <v>1</v>
       </c>
+      <c r="P233" t="n">
+        <v>1</v>
+      </c>
       <c r="Q233" t="n">
         <v>0</v>
       </c>
       <c r="R233" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U233" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -34380,7 +33442,7 @@
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
@@ -34390,12 +33452,7 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ233" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
@@ -34405,11 +33462,6 @@
       </c>
       <c r="AT233" t="n">
         <v>1</v>
-      </c>
-      <c r="AU233" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
@@ -34524,17 +33576,15 @@
       <c r="O234" t="n">
         <v>1</v>
       </c>
+      <c r="P234" t="n">
+        <v>1</v>
+      </c>
       <c r="Q234" t="n">
         <v>0</v>
       </c>
       <c r="R234" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U234" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -34542,7 +33592,7 @@
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
@@ -34552,12 +33602,7 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ234" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
@@ -34567,11 +33612,6 @@
       </c>
       <c r="AT234" t="n">
         <v>1</v>
-      </c>
-      <c r="AU234" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
@@ -34686,17 +33726,15 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
       <c r="Q235" t="n">
         <v>0</v>
       </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U235" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -34704,7 +33742,7 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -34714,12 +33752,7 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ235" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
@@ -34729,11 +33762,6 @@
       </c>
       <c r="AT235" t="n">
         <v>1</v>
-      </c>
-      <c r="AU235" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
@@ -35259,17 +34287,15 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
+      <c r="P239" t="n">
+        <v>0</v>
+      </c>
       <c r="Q239" t="n">
         <v>0</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U239" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -35277,7 +34303,7 @@
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
@@ -35287,12 +34313,7 @@
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
@@ -35302,11 +34323,6 @@
       </c>
       <c r="AT239" t="n">
         <v>1</v>
-      </c>
-      <c r="AU239" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
@@ -35421,17 +34437,15 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
+      <c r="P240" t="n">
+        <v>1</v>
+      </c>
       <c r="Q240" t="n">
         <v>0</v>
       </c>
       <c r="R240" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U240" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -35439,7 +34453,7 @@
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO240" t="inlineStr">
@@ -35449,12 +34463,7 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr">
@@ -35464,11 +34473,6 @@
       </c>
       <c r="AT240" t="n">
         <v>1</v>
-      </c>
-      <c r="AU240" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
@@ -35583,17 +34587,15 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
       <c r="Q241" t="n">
         <v>0</v>
       </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U241" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -35601,7 +34603,7 @@
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO241" t="inlineStr">
@@ -35611,12 +34613,7 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ241" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr">
@@ -35626,11 +34623,6 @@
       </c>
       <c r="AT241" t="n">
         <v>1</v>
-      </c>
-      <c r="AU241" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
@@ -35745,17 +34737,15 @@
       <c r="O242" t="n">
         <v>3</v>
       </c>
+      <c r="P242" t="n">
+        <v>3</v>
+      </c>
       <c r="Q242" t="n">
         <v>0</v>
       </c>
       <c r="R242" t="n">
         <v>0.002353188408904561</v>
       </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U242" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -35763,7 +34753,7 @@
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
@@ -35773,12 +34763,7 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ242" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
@@ -35788,11 +34773,6 @@
       </c>
       <c r="AT242" t="n">
         <v>1</v>
-      </c>
-      <c r="AU242" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
@@ -36318,17 +35298,15 @@
       <c r="O246" t="n">
         <v>5</v>
       </c>
+      <c r="P246" t="n">
+        <v>5</v>
+      </c>
       <c r="Q246" t="n">
         <v>0</v>
       </c>
       <c r="R246" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U246" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -36336,7 +35314,7 @@
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
@@ -36346,12 +35324,7 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ246" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr">
@@ -36361,11 +35334,6 @@
       </c>
       <c r="AT246" t="n">
         <v>1</v>
-      </c>
-      <c r="AU246" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
@@ -36480,17 +35448,15 @@
       <c r="O247" t="n">
         <v>4</v>
       </c>
+      <c r="P247" t="n">
+        <v>4</v>
+      </c>
       <c r="Q247" t="n">
         <v>0</v>
       </c>
       <c r="R247" t="n">
         <v>0.003137584545206081</v>
       </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U247" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -36498,7 +35464,7 @@
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
@@ -36508,12 +35474,7 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ247" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr">
@@ -36523,11 +35484,6 @@
       </c>
       <c r="AT247" t="n">
         <v>1</v>
-      </c>
-      <c r="AU247" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
@@ -36642,17 +35598,15 @@
       <c r="O248" t="n">
         <v>5</v>
       </c>
+      <c r="P248" t="n">
+        <v>5</v>
+      </c>
       <c r="Q248" t="n">
         <v>0</v>
       </c>
       <c r="R248" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U248" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -36660,7 +35614,7 @@
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
@@ -36670,12 +35624,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ248" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr">
@@ -36685,11 +35634,6 @@
       </c>
       <c r="AT248" t="n">
         <v>1</v>
-      </c>
-      <c r="AU248" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
@@ -36804,17 +35748,15 @@
       <c r="O249" t="n">
         <v>6</v>
       </c>
+      <c r="P249" t="n">
+        <v>6</v>
+      </c>
       <c r="Q249" t="n">
         <v>0</v>
       </c>
       <c r="R249" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U249" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -36822,7 +35764,7 @@
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
@@ -36832,12 +35774,7 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ249" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr">
@@ -36847,11 +35784,6 @@
       </c>
       <c r="AT249" t="n">
         <v>1</v>
-      </c>
-      <c r="AU249" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
@@ -36966,17 +35898,15 @@
       <c r="O250" t="n">
         <v>7</v>
       </c>
+      <c r="P250" t="n">
+        <v>7</v>
+      </c>
       <c r="Q250" t="n">
         <v>0</v>
       </c>
       <c r="R250" t="n">
         <v>0.005490772954110641</v>
       </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U250" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -36984,7 +35914,7 @@
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
@@ -36994,12 +35924,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ250" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr">
@@ -37009,11 +35934,6 @@
       </c>
       <c r="AT250" t="n">
         <v>1</v>
-      </c>
-      <c r="AU250" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
@@ -37539,17 +36459,15 @@
       <c r="O254" t="n">
         <v>7</v>
       </c>
+      <c r="P254" t="n">
+        <v>7</v>
+      </c>
       <c r="Q254" t="n">
         <v>0</v>
       </c>
       <c r="R254" t="n">
         <v>0.005490772954110641</v>
       </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U254" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -37557,7 +36475,7 @@
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
@@ -37567,12 +36485,7 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ254" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr">
@@ -37582,11 +36495,6 @@
       </c>
       <c r="AT254" t="n">
         <v>1</v>
-      </c>
-      <c r="AU254" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
@@ -37701,17 +36609,15 @@
       <c r="O255" t="n">
         <v>8</v>
       </c>
+      <c r="P255" t="n">
+        <v>8</v>
+      </c>
       <c r="Q255" t="n">
         <v>0</v>
       </c>
       <c r="R255" t="n">
         <v>0.006275169090412163</v>
       </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U255" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -37719,7 +36625,7 @@
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO255" t="inlineStr">
@@ -37729,12 +36635,7 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ255" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr">
@@ -37744,11 +36645,6 @@
       </c>
       <c r="AT255" t="n">
         <v>1</v>
-      </c>
-      <c r="AU255" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
@@ -37863,17 +36759,15 @@
       <c r="O256" t="n">
         <v>5</v>
       </c>
+      <c r="P256" t="n">
+        <v>5</v>
+      </c>
       <c r="Q256" t="n">
         <v>0</v>
       </c>
       <c r="R256" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U256" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -37881,7 +36775,7 @@
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO256" t="inlineStr">
@@ -37891,12 +36785,7 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ256" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr">
@@ -37906,11 +36795,6 @@
       </c>
       <c r="AT256" t="n">
         <v>1</v>
-      </c>
-      <c r="AU256" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
@@ -38025,17 +36909,15 @@
       <c r="O257" t="n">
         <v>3</v>
       </c>
+      <c r="P257" t="n">
+        <v>3</v>
+      </c>
       <c r="Q257" t="n">
         <v>0</v>
       </c>
       <c r="R257" t="n">
         <v>0.002353188408904561</v>
       </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U257" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -38043,7 +36925,7 @@
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO257" t="inlineStr">
@@ -38053,12 +36935,7 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ257" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr">
@@ -38068,11 +36945,6 @@
       </c>
       <c r="AT257" t="n">
         <v>1</v>
-      </c>
-      <c r="AU257" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
@@ -38598,17 +37470,15 @@
       <c r="O261" t="n">
         <v>2</v>
       </c>
+      <c r="P261" t="n">
+        <v>2</v>
+      </c>
       <c r="Q261" t="n">
         <v>0</v>
       </c>
       <c r="R261" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U261" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -38616,7 +37486,7 @@
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
@@ -38626,12 +37496,7 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ261" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr">
@@ -38641,11 +37506,6 @@
       </c>
       <c r="AT261" t="n">
         <v>1</v>
-      </c>
-      <c r="AU261" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
@@ -38760,17 +37620,15 @@
       <c r="O262" t="n">
         <v>5</v>
       </c>
+      <c r="P262" t="n">
+        <v>5</v>
+      </c>
       <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
         <v>0.003921980681507601</v>
       </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U262" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -38778,7 +37636,7 @@
       </c>
       <c r="AA262" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO262" t="inlineStr">
@@ -38788,12 +37646,7 @@
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ262" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS262" t="inlineStr">
@@ -38803,11 +37656,6 @@
       </c>
       <c r="AT262" t="n">
         <v>1</v>
-      </c>
-      <c r="AU262" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
@@ -38922,17 +37770,15 @@
       <c r="O263" t="n">
         <v>2</v>
       </c>
+      <c r="P263" t="n">
+        <v>2</v>
+      </c>
       <c r="Q263" t="n">
         <v>0</v>
       </c>
       <c r="R263" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S263" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U263" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -38940,7 +37786,7 @@
       </c>
       <c r="AA263" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO263" t="inlineStr">
@@ -38950,12 +37796,7 @@
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ263" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS263" t="inlineStr">
@@ -38965,11 +37806,6 @@
       </c>
       <c r="AT263" t="n">
         <v>1</v>
-      </c>
-      <c r="AU263" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
@@ -39084,17 +37920,15 @@
       <c r="O264" t="n">
         <v>1</v>
       </c>
+      <c r="P264" t="n">
+        <v>1</v>
+      </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U264" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -39102,7 +37936,7 @@
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO264" t="inlineStr">
@@ -39112,12 +37946,7 @@
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS264" t="inlineStr">
@@ -39127,11 +37956,6 @@
       </c>
       <c r="AT264" t="n">
         <v>1</v>
-      </c>
-      <c r="AU264" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
@@ -39384,17 +38208,15 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U266" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -39402,7 +38224,7 @@
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO266" t="inlineStr">
@@ -39412,12 +38234,7 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS266" t="inlineStr">
@@ -39427,11 +38244,6 @@
       </c>
       <c r="AT266" t="n">
         <v>1</v>
-      </c>
-      <c r="AU266" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
@@ -39819,17 +38631,15 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U269" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -39837,7 +38647,7 @@
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO269" t="inlineStr">
@@ -39847,12 +38657,7 @@
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS269" t="inlineStr">
@@ -39862,11 +38667,6 @@
       </c>
       <c r="AT269" t="n">
         <v>1</v>
-      </c>
-      <c r="AU269" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
@@ -39981,17 +38781,15 @@
       <c r="O270" t="n">
         <v>2</v>
       </c>
+      <c r="P270" t="n">
+        <v>2</v>
+      </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U270" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -39999,7 +38797,7 @@
       </c>
       <c r="AA270" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO270" t="inlineStr">
@@ -40009,12 +38807,7 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr">
@@ -40024,11 +38817,6 @@
       </c>
       <c r="AT270" t="n">
         <v>1</v>
-      </c>
-      <c r="AU270" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
@@ -40143,17 +38931,15 @@
       <c r="O271" t="n">
         <v>1</v>
       </c>
+      <c r="P271" t="n">
+        <v>1</v>
+      </c>
       <c r="Q271" t="n">
         <v>0</v>
       </c>
       <c r="R271" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U271" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -40161,7 +38947,7 @@
       </c>
       <c r="AA271" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO271" t="inlineStr">
@@ -40171,12 +38957,7 @@
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS271" t="inlineStr">
@@ -40186,11 +38967,6 @@
       </c>
       <c r="AT271" t="n">
         <v>1</v>
-      </c>
-      <c r="AU271" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
@@ -40305,17 +39081,15 @@
       <c r="O272" t="n">
         <v>1</v>
       </c>
+      <c r="P272" t="n">
+        <v>1</v>
+      </c>
       <c r="Q272" t="n">
         <v>0</v>
       </c>
       <c r="R272" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U272" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -40323,7 +39097,7 @@
       </c>
       <c r="AA272" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO272" t="inlineStr">
@@ -40333,12 +39107,7 @@
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ272" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS272" t="inlineStr">
@@ -40348,11 +39117,6 @@
       </c>
       <c r="AT272" t="n">
         <v>1</v>
-      </c>
-      <c r="AU272" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
@@ -40878,17 +39642,15 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
+      <c r="P276" t="n">
+        <v>0</v>
+      </c>
       <c r="Q276" t="n">
         <v>0</v>
       </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U276" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -40896,7 +39658,7 @@
       </c>
       <c r="AA276" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
@@ -40906,12 +39668,7 @@
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ276" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS276" t="inlineStr">
@@ -40921,11 +39678,6 @@
       </c>
       <c r="AT276" t="n">
         <v>1</v>
-      </c>
-      <c r="AU276" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
@@ -41040,17 +39792,15 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
       <c r="Q277" t="n">
         <v>0</v>
       </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U277" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -41058,7 +39808,7 @@
       </c>
       <c r="AA277" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO277" t="inlineStr">
@@ -41068,12 +39818,7 @@
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ277" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS277" t="inlineStr">
@@ -41083,11 +39828,6 @@
       </c>
       <c r="AT277" t="n">
         <v>1</v>
-      </c>
-      <c r="AU277" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
@@ -41202,17 +39942,15 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
       <c r="Q278" t="n">
         <v>0</v>
       </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
-      <c r="S278" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U278" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -41220,7 +39958,7 @@
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
@@ -41230,12 +39968,7 @@
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ278" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS278" t="inlineStr">
@@ -41245,11 +39978,6 @@
       </c>
       <c r="AT278" t="n">
         <v>1</v>
-      </c>
-      <c r="AU278" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
@@ -41364,17 +40092,15 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
       <c r="Q279" t="n">
         <v>0</v>
       </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U279" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -41382,7 +40108,7 @@
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO279" t="inlineStr">
@@ -41392,12 +40118,7 @@
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ279" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS279" t="inlineStr">
@@ -41407,11 +40128,6 @@
       </c>
       <c r="AT279" t="n">
         <v>1</v>
-      </c>
-      <c r="AU279" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
@@ -41937,17 +40653,15 @@
       <c r="O283" t="n">
         <v>1</v>
       </c>
+      <c r="P283" t="n">
+        <v>1</v>
+      </c>
       <c r="Q283" t="n">
         <v>0</v>
       </c>
       <c r="R283" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S283" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U283" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -41955,7 +40669,7 @@
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO283" t="inlineStr">
@@ -41965,12 +40679,7 @@
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ283" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS283" t="inlineStr">
@@ -41980,11 +40689,6 @@
       </c>
       <c r="AT283" t="n">
         <v>1</v>
-      </c>
-      <c r="AU283" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
@@ -42099,17 +40803,15 @@
       <c r="O284" t="n">
         <v>1</v>
       </c>
+      <c r="P284" t="n">
+        <v>1</v>
+      </c>
       <c r="Q284" t="n">
         <v>0</v>
       </c>
       <c r="R284" t="n">
         <v>0.0007843961363015203</v>
       </c>
-      <c r="S284" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U284" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -42117,7 +40819,7 @@
       </c>
       <c r="AA284" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO284" t="inlineStr">
@@ -42127,12 +40829,7 @@
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ284" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS284" t="inlineStr">
@@ -42142,11 +40839,6 @@
       </c>
       <c r="AT284" t="n">
         <v>1</v>
-      </c>
-      <c r="AU284" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV284" t="inlineStr">
         <is>
@@ -42261,17 +40953,15 @@
       <c r="O285" t="n">
         <v>2</v>
       </c>
+      <c r="P285" t="n">
+        <v>2</v>
+      </c>
       <c r="Q285" t="n">
         <v>0</v>
       </c>
       <c r="R285" t="n">
         <v>0.001568792272603041</v>
       </c>
-      <c r="S285" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U285" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -42279,7 +40969,7 @@
       </c>
       <c r="AA285" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO285" t="inlineStr">
@@ -42289,12 +40979,7 @@
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ285" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS285" t="inlineStr">
@@ -42304,11 +40989,6 @@
       </c>
       <c r="AT285" t="n">
         <v>1</v>
-      </c>
-      <c r="AU285" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
@@ -42423,17 +41103,15 @@
       <c r="O286" t="n">
         <v>6</v>
       </c>
+      <c r="P286" t="n">
+        <v>6</v>
+      </c>
       <c r="Q286" t="n">
         <v>0</v>
       </c>
       <c r="R286" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S286" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U286" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -42441,7 +41119,7 @@
       </c>
       <c r="AA286" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO286" t="inlineStr">
@@ -42451,12 +41129,7 @@
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ286" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS286" t="inlineStr">
@@ -42466,11 +41139,6 @@
       </c>
       <c r="AT286" t="n">
         <v>1</v>
-      </c>
-      <c r="AU286" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV286" t="inlineStr">
         <is>
@@ -42585,17 +41253,15 @@
       <c r="O287" t="n">
         <v>9</v>
       </c>
+      <c r="P287" t="n">
+        <v>9</v>
+      </c>
       <c r="Q287" t="n">
         <v>0</v>
       </c>
       <c r="R287" t="n">
         <v>0.007059565226713681</v>
       </c>
-      <c r="S287" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U287" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -42603,7 +41269,7 @@
       </c>
       <c r="AA287" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO287" t="inlineStr">
@@ -42613,12 +41279,7 @@
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ287" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS287" t="inlineStr">
@@ -42628,11 +41289,6 @@
       </c>
       <c r="AT287" t="n">
         <v>1</v>
-      </c>
-      <c r="AU287" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV287" t="inlineStr">
         <is>
@@ -43158,17 +41814,15 @@
       <c r="O291" t="n">
         <v>6</v>
       </c>
+      <c r="P291" t="n">
+        <v>6</v>
+      </c>
       <c r="Q291" t="n">
         <v>0</v>
       </c>
       <c r="R291" t="n">
         <v>0.004706376817809122</v>
       </c>
-      <c r="S291" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U291" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -43176,7 +41830,7 @@
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO291" t="inlineStr">
@@ -43186,12 +41840,7 @@
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ291" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS291" t="inlineStr">
@@ -43201,11 +41850,6 @@
       </c>
       <c r="AT291" t="n">
         <v>1</v>
-      </c>
-      <c r="AU291" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV291" t="inlineStr">
         <is>
@@ -43320,17 +41964,15 @@
       <c r="O292" t="n">
         <v>20</v>
       </c>
+      <c r="P292" t="n">
+        <v>20</v>
+      </c>
       <c r="Q292" t="n">
         <v>0</v>
       </c>
       <c r="R292" t="n">
         <v>0.0156879227260304</v>
       </c>
-      <c r="S292" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U292" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -43338,7 +41980,7 @@
       </c>
       <c r="AA292" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO292" t="inlineStr">
@@ -43348,12 +41990,7 @@
       </c>
       <c r="AP292" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ292" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS292" t="inlineStr">
@@ -43363,11 +42000,6 @@
       </c>
       <c r="AT292" t="n">
         <v>1</v>
-      </c>
-      <c r="AU292" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV292" t="inlineStr">
         <is>
@@ -43482,17 +42114,15 @@
       <c r="O293" t="n">
         <v>21</v>
       </c>
+      <c r="P293" t="n">
+        <v>21</v>
+      </c>
       <c r="Q293" t="n">
         <v>0</v>
       </c>
       <c r="R293" t="n">
         <v>0.01647231886233192</v>
       </c>
-      <c r="S293" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U293" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -43500,7 +42130,7 @@
       </c>
       <c r="AA293" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO293" t="inlineStr">
@@ -43510,12 +42140,7 @@
       </c>
       <c r="AP293" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ293" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS293" t="inlineStr">
@@ -43525,11 +42150,6 @@
       </c>
       <c r="AT293" t="n">
         <v>1</v>
-      </c>
-      <c r="AU293" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV293" t="inlineStr">
         <is>
@@ -43644,17 +42264,15 @@
       <c r="O294" t="n">
         <v>15</v>
       </c>
+      <c r="P294" t="n">
+        <v>15</v>
+      </c>
       <c r="Q294" t="n">
         <v>0</v>
       </c>
       <c r="R294" t="n">
         <v>0.0117659420445228</v>
       </c>
-      <c r="S294" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U294" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -43662,7 +42280,7 @@
       </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO294" t="inlineStr">
@@ -43672,12 +42290,7 @@
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ294" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS294" t="inlineStr">
@@ -43687,11 +42300,6 @@
       </c>
       <c r="AT294" t="n">
         <v>1</v>
-      </c>
-      <c r="AU294" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV294" t="inlineStr">
         <is>
@@ -44217,17 +42825,15 @@
       <c r="O298" t="n">
         <v>15</v>
       </c>
+      <c r="P298" t="n">
+        <v>15</v>
+      </c>
       <c r="Q298" t="n">
         <v>0</v>
       </c>
       <c r="R298" t="n">
         <v>0.0117659420445228</v>
       </c>
-      <c r="S298" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U298" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -44235,7 +42841,7 @@
       </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO298" t="inlineStr">
@@ -44245,12 +42851,7 @@
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ298" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS298" t="inlineStr">
@@ -44260,11 +42861,6 @@
       </c>
       <c r="AT298" t="n">
         <v>1</v>
-      </c>
-      <c r="AU298" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
@@ -44379,17 +42975,15 @@
       <c r="O299" t="n">
         <v>18</v>
       </c>
+      <c r="P299" t="n">
+        <v>18</v>
+      </c>
       <c r="Q299" t="n">
         <v>0</v>
       </c>
       <c r="R299" t="n">
         <v>0.01411913045342736</v>
       </c>
-      <c r="S299" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U299" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -44397,7 +42991,7 @@
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO299" t="inlineStr">
@@ -44407,12 +43001,7 @@
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ299" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr">
@@ -44422,11 +43011,6 @@
       </c>
       <c r="AT299" t="n">
         <v>1</v>
-      </c>
-      <c r="AU299" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
@@ -44541,17 +43125,15 @@
       <c r="O300" t="n">
         <v>14</v>
       </c>
+      <c r="P300" t="n">
+        <v>14</v>
+      </c>
       <c r="Q300" t="n">
         <v>0</v>
       </c>
       <c r="R300" t="n">
         <v>0.01098154590822128</v>
       </c>
-      <c r="S300" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U300" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -44559,7 +43141,7 @@
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO300" t="inlineStr">
@@ -44569,12 +43151,7 @@
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ300" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS300" t="inlineStr">
@@ -44584,11 +43161,6 @@
       </c>
       <c r="AT300" t="n">
         <v>1</v>
-      </c>
-      <c r="AU300" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
@@ -44703,17 +43275,15 @@
       <c r="O301" t="n">
         <v>13</v>
       </c>
+      <c r="P301" t="n">
+        <v>13</v>
+      </c>
       <c r="Q301" t="n">
         <v>0</v>
       </c>
       <c r="R301" t="n">
         <v>0.01019714977191976</v>
       </c>
-      <c r="S301" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U301" t="inlineStr">
         <is>
           <t>HOLD_JP_9e2aab276be221d6aeb32112cab2</t>
@@ -44721,7 +43291,7 @@
       </c>
       <c r="AA301" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO301" t="inlineStr">
@@ -44731,12 +43301,7 @@
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ301" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS301" t="inlineStr">
@@ -44746,11 +43311,6 @@
       </c>
       <c r="AT301" t="n">
         <v>1</v>
-      </c>
-      <c r="AU301" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>

--- a/diseases/d058/2010-2014.xlsx
+++ b/diseases/d058/2010-2014.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>0.04716078490514505</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,12 +938,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1182,6 +1212,11 @@
       <c r="R5" t="n">
         <v>0.01408130007574331</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1194,12 +1229,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1317,6 +1362,11 @@
       <c r="R6" t="n">
         <v>0.02665609581595155</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1329,12 +1379,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1593,6 +1653,11 @@
       <c r="R8" t="n">
         <v>0.02816260015148662</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1605,12 +1670,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1728,6 +1803,11 @@
       <c r="R9" t="n">
         <v>0.02255515799811285</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1740,12 +1820,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2004,6 +2094,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2016,12 +2111,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2139,6 +2244,11 @@
       <c r="R12" t="n">
         <v>0.0328075025427096</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2151,12 +2261,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2415,6 +2535,11 @@
       <c r="R14" t="n">
         <v>0.04224390022722994</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2427,12 +2552,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2550,6 +2685,11 @@
       <c r="R15" t="n">
         <v>0.05536266054082245</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2562,12 +2702,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2826,6 +2976,11 @@
       <c r="R17" t="n">
         <v>0.04224390022722994</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2838,12 +2993,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2961,6 +3126,11 @@
       <c r="R18" t="n">
         <v>0.05536266054082245</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2973,12 +3143,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3237,6 +3417,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3249,12 +3434,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3372,6 +3567,11 @@
       <c r="R21" t="n">
         <v>0.05536266054082245</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3384,12 +3584,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3648,6 +3858,11 @@
       <c r="R23" t="n">
         <v>0.05632520030297325</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3660,12 +3875,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3783,6 +4008,11 @@
       <c r="R24" t="n">
         <v>0.05536266054082245</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3795,12 +4025,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4059,6 +4299,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4071,12 +4316,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4194,6 +4449,11 @@
       <c r="R27" t="n">
         <v>0.123028134535161</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4206,12 +4466,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4470,6 +4740,11 @@
       <c r="R29" t="n">
         <v>0.01408130007574331</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4482,12 +4757,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4605,6 +4890,11 @@
       <c r="R30" t="n">
         <v>2.466714097429978</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4617,12 +4907,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4881,6 +5181,11 @@
       <c r="R32" t="n">
         <v>0.04224390022722994</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4893,12 +5198,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5016,6 +5331,11 @@
       <c r="R33" t="n">
         <v>7.857396858978949</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5028,12 +5348,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5292,6 +5622,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5304,12 +5639,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5427,6 +5772,11 @@
       <c r="R36" t="n">
         <v>0.8304399081123368</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5439,12 +5789,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5703,6 +6063,11 @@
       <c r="R38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5715,12 +6080,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5838,6 +6213,11 @@
       <c r="R39" t="n">
         <v>0.07531401338230277</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5850,12 +6230,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6114,6 +6504,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6126,12 +6521,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6249,6 +6654,11 @@
       <c r="R42" t="n">
         <v>0.0223906526271711</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6261,12 +6671,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6525,6 +6945,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6537,12 +6962,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6660,6 +7095,11 @@
       <c r="R45" t="n">
         <v>0.02035513875197372</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6672,12 +7112,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6936,6 +7386,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6948,12 +7403,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7071,6 +7536,11 @@
       <c r="R48" t="n">
         <v>0.02646168037756584</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7083,12 +7553,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7347,6 +7827,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7359,12 +7844,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7482,6 +7977,11 @@
       <c r="R51" t="n">
         <v>0.05088784687993431</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7494,12 +7994,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7758,6 +8268,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7770,12 +8285,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -7893,6 +8418,11 @@
       <c r="R54" t="n">
         <v>0.04885233300473694</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7905,12 +8435,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8169,6 +8709,11 @@
       <c r="R56" t="n">
         <v>0.01399977978346401</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8181,12 +8726,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8304,6 +8859,11 @@
       <c r="R57" t="n">
         <v>0.03663924975355271</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8316,12 +8876,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8580,6 +9150,11 @@
       <c r="R59" t="n">
         <v>0.01399977978346401</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8592,12 +9167,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8715,6 +9300,11 @@
       <c r="R60" t="n">
         <v>0.05699438850552643</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8727,12 +9317,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -8991,6 +9591,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9003,12 +9608,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9126,6 +9741,11 @@
       <c r="R63" t="n">
         <v>0.1567345683901977</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9138,12 +9758,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9402,6 +10032,11 @@
       <c r="R65" t="n">
         <v>0.02799955956692802</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9414,12 +10049,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9537,6 +10182,11 @@
       <c r="R66" t="n">
         <v>3.714812822235205</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9549,12 +10199,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -9813,6 +10473,11 @@
       <c r="R68" t="n">
         <v>0.01399977978346401</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9825,12 +10490,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -9948,6 +10623,11 @@
       <c r="R69" t="n">
         <v>5.532526712786458</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9960,12 +10640,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10224,6 +10914,11 @@
       <c r="R71" t="n">
         <v>0.02799955956692802</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10236,12 +10931,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10359,6 +11064,11 @@
       <c r="R72" t="n">
         <v>0.7429625644470409</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10371,12 +11081,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10635,6 +11355,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10647,12 +11372,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -10770,6 +11505,11 @@
       <c r="R75" t="n">
         <v>0.1028234523641476</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10782,12 +11522,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11046,6 +11796,11 @@
       <c r="R77" t="n">
         <v>0.01388684250834703</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11058,12 +11813,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11181,6 +11946,11 @@
       <c r="R78" t="n">
         <v>0.08266199111627549</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11193,12 +11963,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11457,6 +12237,11 @@
       <c r="R80" t="n">
         <v>0.02777368501669407</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11469,12 +12254,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -11592,6 +12387,11 @@
       <c r="R81" t="n">
         <v>0.03024219187180811</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11604,12 +12404,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -11868,6 +12678,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11880,12 +12695,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12003,6 +12828,11 @@
       <c r="R84" t="n">
         <v>0.03427448412138252</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12015,12 +12845,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12279,6 +13119,11 @@
       <c r="R86" t="n">
         <v>0.01388684250834703</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12291,12 +13136,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12414,6 +13269,11 @@
       <c r="R87" t="n">
         <v>0.04032292249574414</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12426,12 +13286,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12690,6 +13560,11 @@
       <c r="R89" t="n">
         <v>0.09720789755842922</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12702,12 +13577,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -12825,6 +13710,11 @@
       <c r="R90" t="n">
         <v>0.0282260457470209</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12837,12 +13727,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13101,6 +14001,11 @@
       <c r="R92" t="n">
         <v>0.0416605275250411</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13113,12 +14018,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13236,6 +14151,11 @@
       <c r="R93" t="n">
         <v>0.05040365311968018</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13248,12 +14168,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13512,6 +14442,11 @@
       <c r="R95" t="n">
         <v>0.05554737003338813</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13524,12 +14459,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -13647,6 +14592,11 @@
       <c r="R96" t="n">
         <v>0.07258126049233946</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13659,12 +14609,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -13923,6 +14883,11 @@
       <c r="R98" t="n">
         <v>0.01388684250834703</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13935,12 +14900,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14058,6 +15033,11 @@
       <c r="R99" t="n">
         <v>0.2056469047282951</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14070,12 +15050,22 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -14784,6 +15774,11 @@
       <c r="R104" t="n">
         <v>0.02777368501669407</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14796,12 +15791,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -14919,6 +15924,11 @@
       <c r="R105" t="n">
         <v>7.419417739216922</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14931,12 +15941,22 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15795,6 +16815,11 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15807,12 +16832,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -15930,6 +16965,11 @@
       <c r="R112" t="n">
         <v>8.752090327701266</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15942,12 +16982,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -16956,6 +18006,11 @@
       <c r="R119" t="n">
         <v>0.02777368501669407</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16968,12 +18023,22 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -17091,6 +18156,11 @@
       <c r="R120" t="n">
         <v>0.5282302846942483</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17103,12 +18173,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -17967,6 +19047,11 @@
       <c r="R126" t="n">
         <v>0.02753176994177719</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17979,12 +19064,22 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -18102,6 +19197,11 @@
       <c r="R127" t="n">
         <v>0.0499289366437643</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18114,12 +19214,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -18978,6 +20088,11 @@
       <c r="R133" t="n">
         <v>0.02753176994177719</v>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18990,12 +20105,22 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -19263,6 +20388,11 @@
       <c r="R135" t="n">
         <v>0.03195451945200915</v>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19275,12 +20405,22 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -19989,6 +21129,11 @@
       <c r="R140" t="n">
         <v>0.08259530982533157</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20001,12 +21146,22 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -20274,6 +21429,11 @@
       <c r="R142" t="n">
         <v>0.01198294479450343</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20286,12 +21446,22 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -21150,6 +22320,11 @@
       <c r="R148" t="n">
         <v>0</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21162,12 +22337,22 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -21285,6 +22470,11 @@
       <c r="R149" t="n">
         <v>0.01797441719175515</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21297,12 +22487,22 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -22161,6 +23361,11 @@
       <c r="R155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22173,12 +23378,22 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -22296,6 +23511,11 @@
       <c r="R156" t="n">
         <v>0.05991472397251715</v>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22308,12 +23528,22 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -23322,6 +24552,11 @@
       <c r="R163" t="n">
         <v>0.06882942485444297</v>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23334,12 +24569,22 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -23457,6 +24702,11 @@
       <c r="R164" t="n">
         <v>0.06191188143826773</v>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23469,12 +24719,22 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -24333,6 +25593,11 @@
       <c r="R170" t="n">
         <v>0.05506353988355438</v>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24345,12 +25610,22 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -24468,6 +25743,11 @@
       <c r="R171" t="n">
         <v>0.0778891411642723</v>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24480,12 +25760,22 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -25344,6 +26634,11 @@
       <c r="R177" t="n">
         <v>0.0137658849708886</v>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25356,12 +26651,22 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -25479,6 +26784,11 @@
       <c r="R178" t="n">
         <v>0.05192609410951488</v>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25491,12 +26801,22 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -26505,6 +27825,11 @@
       <c r="R185" t="n">
         <v>0.04129765491266579</v>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26517,12 +27842,22 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -26640,6 +27975,11 @@
       <c r="R186" t="n">
         <v>0.1497868099312929</v>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26652,12 +27992,22 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -27516,6 +28866,11 @@
       <c r="R192" t="n">
         <v>0.04129765491266579</v>
       </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27528,12 +28883,22 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
@@ -27651,6 +29016,11 @@
       <c r="R193" t="n">
         <v>7.30160769478409</v>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27663,12 +29033,22 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
@@ -28527,6 +29907,11 @@
       <c r="R199" t="n">
         <v>0.02753176994177719</v>
       </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28539,12 +29924,22 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
@@ -28812,6 +30207,11 @@
       <c r="R201" t="n">
         <v>12.06682540806496</v>
       </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28824,12 +30224,22 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
         <v>0</v>
+      </c>
+      <c r="AU201" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
@@ -29688,6 +31098,11 @@
       <c r="R207" t="n">
         <v>0</v>
       </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29700,12 +31115,22 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR207" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
         <v>0</v>
+      </c>
+      <c r="AU207" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
@@ -29823,6 +31248,11 @@
       <c r="R208" t="n">
         <v>0.8188345609577344</v>
       </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29835,12 +31265,22 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
         <v>0</v>
+      </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
@@ -30699,6 +32139,11 @@
       <c r="R214" t="n">
         <v>0</v>
       </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30711,12 +32156,22 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR214" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
         <v>0</v>
+      </c>
+      <c r="AU214" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
@@ -30834,6 +32289,11 @@
       <c r="R215" t="n">
         <v>0.06727470401578835</v>
       </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30846,12 +32306,22 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR215" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
         <v>0</v>
+      </c>
+      <c r="AU215" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
@@ -31860,6 +33330,11 @@
       <c r="R222" t="n">
         <v>0.01366213445849208</v>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31872,12 +33347,22 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
         <v>0</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
@@ -31995,6 +33480,11 @@
       <c r="R223" t="n">
         <v>0.02374401318204294</v>
       </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32007,12 +33497,22 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
@@ -32871,6 +34371,11 @@
       <c r="R229" t="n">
         <v>0.02732426891698416</v>
       </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32883,12 +34388,22 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr"/>
       <c r="AT229" t="n">
         <v>0</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
@@ -33006,6 +34521,11 @@
       <c r="R230" t="n">
         <v>0.03759468753823466</v>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33018,12 +34538,22 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
@@ -33882,6 +35412,11 @@
       <c r="R236" t="n">
         <v>0</v>
       </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33894,12 +35429,22 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
         <v>0</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
@@ -34017,6 +35562,11 @@
       <c r="R237" t="n">
         <v>0.05342402965959663</v>
       </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34029,12 +35579,22 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
         <v>0</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
@@ -34893,6 +36453,11 @@
       <c r="R243" t="n">
         <v>0</v>
       </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34905,12 +36470,22 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
         <v>0</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
@@ -35028,6 +36603,11 @@
       <c r="R244" t="n">
         <v>0.08904004943266104</v>
       </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35040,12 +36620,22 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
         <v>0</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
@@ -36054,6 +37644,11 @@
       <c r="R251" t="n">
         <v>0.05464853783396832</v>
       </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36066,12 +37661,22 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
         <v>0</v>
+      </c>
+      <c r="AU251" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
@@ -36189,6 +37794,11 @@
       <c r="R252" t="n">
         <v>0.05342402965959663</v>
       </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36201,12 +37811,22 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
         <v>0</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
@@ -37065,6 +38685,11 @@
       <c r="R258" t="n">
         <v>0.08197280675095248</v>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37077,12 +38702,22 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
         <v>0</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
@@ -37200,6 +38835,11 @@
       <c r="R259" t="n">
         <v>0.07321070731129908</v>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37212,12 +38852,22 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
         <v>0</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
@@ -38076,6 +39726,11 @@
       <c r="R265" t="n">
         <v>0.01366213445849208</v>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38088,12 +39743,22 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
         <v>0</v>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
@@ -38361,6 +40026,11 @@
       <c r="R267" t="n">
         <v>0.09299738496300154</v>
       </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38373,12 +40043,22 @@
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
         <v>0</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
@@ -39237,6 +40917,11 @@
       <c r="R273" t="n">
         <v>0.02732426891698416</v>
       </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39249,12 +40934,22 @@
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
         <v>0</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
@@ -39372,6 +41067,11 @@
       <c r="R274" t="n">
         <v>0.5124749511790936</v>
       </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA274" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39384,12 +41084,22 @@
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS274" t="inlineStr"/>
       <c r="AT274" t="n">
         <v>0</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
@@ -40248,6 +41958,11 @@
       <c r="R280" t="n">
         <v>0.01366213445849208</v>
       </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40260,12 +41975,22 @@
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS280" t="inlineStr"/>
       <c r="AT280" t="n">
         <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
@@ -40383,6 +42108,11 @@
       <c r="R281" t="n">
         <v>8.045263133182218</v>
       </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40395,12 +42125,22 @@
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS281" t="inlineStr"/>
       <c r="AT281" t="n">
         <v>0</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
@@ -41409,6 +43149,11 @@
       <c r="R288" t="n">
         <v>0.02732426891698416</v>
       </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41421,12 +43166,22 @@
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS288" t="inlineStr"/>
       <c r="AT288" t="n">
         <v>0</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
@@ -41544,6 +43299,11 @@
       <c r="R289" t="n">
         <v>6.533560960592149</v>
       </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA289" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41556,12 +43316,22 @@
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS289" t="inlineStr"/>
       <c r="AT289" t="n">
         <v>0</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV289" t="inlineStr">
         <is>
@@ -42420,6 +44190,11 @@
       <c r="R295" t="n">
         <v>0</v>
       </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA295" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42432,12 +44207,22 @@
       </c>
       <c r="AP295" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR295" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS295" t="inlineStr"/>
       <c r="AT295" t="n">
         <v>0</v>
+      </c>
+      <c r="AU295" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV295" t="inlineStr">
         <is>
@@ -42555,6 +44340,11 @@
       <c r="R296" t="n">
         <v>0.5045602801184126</v>
       </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA296" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42567,12 +44357,22 @@
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS296" t="inlineStr"/>
       <c r="AT296" t="n">
         <v>0</v>
+      </c>
+      <c r="AU296" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV296" t="inlineStr">
         <is>
